--- a/AVIATIONprocessing/SliceVelocityValidation/SSWT_SliceUxValidation_FigureData.xlsx
+++ b/AVIATIONprocessing/SliceVelocityValidation/SSWT_SliceUxValidation_FigureData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Boller CFD\GitHub\CFDPostprocessingCodes\AVIATIONprocessing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Boller CFD\GitHub\CFDPostprocessingCodes\AVIATIONprocessing\SliceVelocityValidation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3BDDD5-7965-4859-839A-5D87ADA6F6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801E186B-50EC-4E9F-9D0D-39817D57CF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5685" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{12DF1E63-F8AF-48B4-87CD-AC55BD68FC80}"/>
   </bookViews>
@@ -42,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="8">
   <si>
-    <t>Volcano</t>
-  </si>
-  <si>
     <t>VULCAN</t>
   </si>
   <si>
@@ -64,6 +61,9 @@
   </si>
   <si>
     <t>Fureby et. al.</t>
+  </si>
+  <si>
+    <t>Volcano Slice</t>
   </si>
 </sst>
 </file>
@@ -431,51 +431,51 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
         <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>6.6047118155619592E-3</v>
+        <v>-4.3227665706051875E-2</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -501,10 +501,10 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>3.2452881844380402E-3</v>
+        <v>-4.1818587896253596E-2</v>
       </c>
       <c r="C5">
-        <v>-0.98396793587174336</v>
+        <v>-0.97979797979797989</v>
       </c>
       <c r="E5">
         <v>-7.6602762000000005E-2</v>
@@ -527,10 +527,10 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>4.7997406340057638E-4</v>
+        <v>-5.2041786743515846E-2</v>
       </c>
       <c r="C6">
-        <v>-0.97194388777555107</v>
+        <v>-0.95959595959595956</v>
       </c>
       <c r="E6">
         <v>-6.7252113000000002E-2</v>
@@ -553,10 +553,10 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>-2.0024639769452451E-3</v>
+        <v>-5.8795244956772331E-2</v>
       </c>
       <c r="C7">
-        <v>-0.95991983967935868</v>
+        <v>-0.93939393939393945</v>
       </c>
       <c r="E7">
         <v>-5.4702122999999998E-2</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>-4.4124639769452453E-3</v>
+        <v>-6.6152449567723343E-2</v>
       </c>
       <c r="C8">
-        <v>-0.94388777555110226</v>
+        <v>-0.91919191919191912</v>
       </c>
       <c r="E8">
         <v>-5.4900021E-2</v>
@@ -605,10 +605,10 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>-6.5594668587896253E-3</v>
+        <v>-7.0072478386167147E-2</v>
       </c>
       <c r="C9">
-        <v>-0.93186372745490986</v>
+        <v>-0.89898989898989901</v>
       </c>
       <c r="E9">
         <v>-4.873222E-2</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>-8.6555187319884725E-3</v>
+        <v>-7.332420749279539E-2</v>
       </c>
       <c r="C10">
-        <v>-0.91583166332665333</v>
+        <v>-0.8787878787878789</v>
       </c>
       <c r="E10">
         <v>-3.2982890000000001E-2</v>
@@ -657,10 +657,10 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>-1.0548256484149856E-2</v>
+        <v>-7.6107925072046112E-2</v>
       </c>
       <c r="C11">
-        <v>-0.90380761523046094</v>
+        <v>-0.85858585858585856</v>
       </c>
       <c r="E11">
         <v>-3.3156049999999999E-2</v>
@@ -683,10 +683,10 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>-1.228693083573487E-2</v>
+        <v>-8.0145821325648417E-2</v>
       </c>
       <c r="C12">
-        <v>-0.89178356713426854</v>
+        <v>-0.83838383838383845</v>
       </c>
       <c r="E12">
         <v>-3.3304473000000001E-2</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>-1.3837334293948126E-2</v>
+        <v>-8.2515273775216141E-2</v>
       </c>
       <c r="C13">
-        <v>-0.87575150300601201</v>
+        <v>-0.81818181818181823</v>
       </c>
       <c r="E13">
         <v>-3.9802102999999998E-2</v>
@@ -735,10 +735,10 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>-1.5587463976945246E-2</v>
+        <v>-8.4290201729106631E-2</v>
       </c>
       <c r="C14">
-        <v>-0.86372745490981961</v>
+        <v>-0.79797979797979801</v>
       </c>
       <c r="E14">
         <v>-3.3568335999999997E-2</v>
@@ -761,10 +761,10 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>-1.7172910662824205E-2</v>
+        <v>-8.5737175792507211E-2</v>
       </c>
       <c r="C15">
-        <v>-0.85170340681362722</v>
+        <v>-0.77777777777777779</v>
       </c>
       <c r="E15">
         <v>-3.3725005000000002E-2</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>-1.9585158501440922E-2</v>
+        <v>-8.7754034582132559E-2</v>
       </c>
       <c r="C16">
-        <v>-0.8236472945891784</v>
+        <v>-0.75757575757575757</v>
       </c>
       <c r="E16">
         <v>-3.0682333999999999E-2</v>
@@ -813,10 +813,10 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>-2.155907780979827E-2</v>
+        <v>-8.8787608069164262E-2</v>
       </c>
       <c r="C17">
-        <v>-0.81162324649298589</v>
+        <v>-0.73737373737373746</v>
       </c>
       <c r="E17">
         <v>-3.7171717E-2</v>
@@ -839,10 +839,10 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>-2.346484149855908E-2</v>
+        <v>-8.9523775216138329E-2</v>
       </c>
       <c r="C18">
-        <v>-0.78356713426853708</v>
+        <v>-0.71717171717171713</v>
       </c>
       <c r="E18">
         <v>-3.7303649000000001E-2</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>-2.4431700288184439E-2</v>
+        <v>-9.013429394812679E-2</v>
       </c>
       <c r="C19">
-        <v>-0.75551102204408815</v>
+        <v>-0.69696969696969702</v>
       </c>
       <c r="E19">
         <v>-4.3793032000000003E-2</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>-2.4974927953890488E-2</v>
+        <v>-9.0666570605187319E-2</v>
       </c>
       <c r="C20">
-        <v>-0.73146292585170325</v>
+        <v>-0.6767676767676768</v>
       </c>
       <c r="E20">
         <v>-4.0766851999999999E-2</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>-2.4809798270893371E-2</v>
+        <v>-9.0799423631123921E-2</v>
       </c>
       <c r="C21">
-        <v>-0.70340681362725455</v>
+        <v>-0.65656565656565657</v>
       </c>
       <c r="E21">
         <v>-3.4582559999999998E-2</v>
@@ -943,10 +943,10 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>-2.5275648414985589E-2</v>
+        <v>-9.0724351585014407E-2</v>
       </c>
       <c r="C22">
-        <v>-0.67535070140280551</v>
+        <v>-0.63636363636363646</v>
       </c>
       <c r="E22">
         <v>-2.8340548E-2</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>-2.4317723342939482E-2</v>
+        <v>-9.0564697406340058E-2</v>
       </c>
       <c r="C23">
-        <v>-0.64729458917835681</v>
+        <v>-0.61616161616161613</v>
       </c>
       <c r="E23">
         <v>-1.5765820999999999E-2</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>-2.4226368876080689E-2</v>
+        <v>-8.988472622478387E-2</v>
       </c>
       <c r="C24">
-        <v>-0.6232464929859719</v>
+        <v>-0.59595959595959602</v>
       </c>
       <c r="E24">
         <v>-3.240569E-3</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>-2.2198270893371758E-2</v>
+        <v>-8.9203025936599428E-2</v>
       </c>
       <c r="C25">
-        <v>-0.59519038076152309</v>
+        <v>-0.5757575757575758</v>
       </c>
       <c r="E25">
         <v>3.7913832000000001E-2</v>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>-2.0702161383285303E-2</v>
+        <v>-8.8237896253602302E-2</v>
       </c>
       <c r="C26">
-        <v>-0.56713426853707416</v>
+        <v>-0.55555555555555558</v>
       </c>
       <c r="E26">
         <v>8.2317048000000004E-2</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>-1.8297118155619598E-2</v>
+        <v>-8.6985734870316994E-2</v>
       </c>
       <c r="C27">
-        <v>-0.54308617234468937</v>
+        <v>-0.53535353535353536</v>
       </c>
       <c r="E27">
         <v>0.12356215199999999</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>-1.7004899135446686E-2</v>
+        <v>-8.5821037463976943E-2</v>
       </c>
       <c r="C28">
-        <v>-0.51503006012024044</v>
+        <v>-0.51515151515151525</v>
       </c>
       <c r="E28">
         <v>0.16479076500000001</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>-1.4565561959654178E-2</v>
+        <v>-8.4464841498559082E-2</v>
       </c>
       <c r="C29">
-        <v>-0.48697394789579163</v>
+        <v>-0.49494949494949497</v>
       </c>
       <c r="E29">
         <v>0.20921047200000001</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>-1.2932449567723344E-2</v>
+        <v>-8.3244380403458218E-2</v>
       </c>
       <c r="C30">
-        <v>-0.45891783567134259</v>
+        <v>-0.47474747474747492</v>
       </c>
       <c r="E30">
         <v>0.27266130700000002</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>-1.0150403458213256E-2</v>
+        <v>-8.1440778097982711E-2</v>
       </c>
       <c r="C31">
-        <v>-0.4348697394789578</v>
+        <v>-0.45454545454545442</v>
       </c>
       <c r="E31">
         <v>0.339311482</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>-8.9613976945244964E-3</v>
+        <v>-7.98014409221902E-2</v>
       </c>
       <c r="C32">
-        <v>-0.40681362725450898</v>
+        <v>-0.43434343434343442</v>
       </c>
       <c r="E32">
         <v>0.41545248400000001</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>-5.8786743515850141E-3</v>
+        <v>-7.8402593659942357E-2</v>
       </c>
       <c r="C33">
-        <v>-0.37875751503006022</v>
+        <v>-0.41414141414141431</v>
       </c>
       <c r="E33">
         <v>0.47256235800000002</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>-4.4612103746397699E-3</v>
+        <v>-7.5882276657060516E-2</v>
       </c>
       <c r="C34">
-        <v>-0.35470941883767543</v>
+        <v>-0.39393939393939392</v>
       </c>
       <c r="E34">
         <v>0.526489384</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>-1.5494956772334294E-3</v>
+        <v>-7.426296829971181E-2</v>
       </c>
       <c r="C35">
-        <v>-0.32665330661322639</v>
+        <v>-0.37373737373737381</v>
       </c>
       <c r="E35">
         <v>0.58359925800000001</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>-2.1432853025936597E-4</v>
+        <v>-7.2234438040345822E-2</v>
       </c>
       <c r="C36">
-        <v>-0.29859719438877758</v>
+        <v>-0.35353535353535342</v>
       </c>
       <c r="E36">
         <v>0.63436817199999995</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>2.9788328530259366E-3</v>
+        <v>-7.0092507204610952E-2</v>
       </c>
       <c r="C37">
-        <v>-0.27054108216432871</v>
+        <v>-0.33333333333333331</v>
       </c>
       <c r="E37">
         <v>0.68196248199999998</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>3.3479250720461094E-3</v>
+        <v>-6.6877089337175788E-2</v>
       </c>
       <c r="C38">
-        <v>-0.24649298597194369</v>
+        <v>-0.31313131313131332</v>
       </c>
       <c r="E38">
         <v>0.72320758600000001</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>5.7576080691642646E-3</v>
+        <v>-6.4993227665706046E-2</v>
       </c>
       <c r="C39">
-        <v>-0.2184368737474951</v>
+        <v>-0.29292929292929287</v>
       </c>
       <c r="E39">
         <v>0.76442795299999999</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>5.2446253602305478E-3</v>
+        <v>-6.273602305475505E-2</v>
       </c>
       <c r="C40">
-        <v>-0.190380761523046</v>
+        <v>-0.27272727272727282</v>
       </c>
       <c r="E40">
         <v>0.81518037499999996</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>6.9985734870316998E-3</v>
+        <v>-6.0581123919308359E-2</v>
       </c>
       <c r="C41">
-        <v>-0.16633266533066141</v>
+        <v>-0.25252525252525237</v>
       </c>
       <c r="E41">
         <v>0.84367759200000003</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>7.4231700288184439E-3</v>
+        <v>-5.6690201729106632E-2</v>
       </c>
       <c r="C42">
-        <v>-0.13827655310621231</v>
+        <v>-0.23232323232323229</v>
       </c>
       <c r="E42">
         <v>0.87849103299999998</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>2.0991930835734873E-2</v>
+        <v>-5.4045389048991352E-2</v>
       </c>
       <c r="C43">
-        <v>-0.1102204408817635</v>
+        <v>-0.21212121212121199</v>
       </c>
       <c r="E43">
         <v>0.91014636199999999</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>6.5279971181556193E-2</v>
+        <v>-5.1077809798270896E-2</v>
       </c>
       <c r="C44">
-        <v>-8.2164328657314586E-2</v>
+        <v>-0.19191919191919191</v>
       </c>
       <c r="E44">
         <v>0.92908678600000005</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>0.16538184438040346</v>
+        <v>-4.7011383285302598E-2</v>
       </c>
       <c r="C45">
-        <v>-5.8116232464929862E-2</v>
+        <v>-0.17171717171717171</v>
       </c>
       <c r="E45">
         <v>0.94483611599999995</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>0.30534582132564841</v>
+        <v>-3.7160806916426516E-2</v>
       </c>
       <c r="C46">
-        <v>-3.0060120240481089E-2</v>
+        <v>-0.15151515151515149</v>
       </c>
       <c r="E46">
         <v>0.957394352</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>0.50433717579250714</v>
+        <v>-2.4653602305475506E-2</v>
       </c>
       <c r="C47">
-        <v>-2.0040080160317491E-3</v>
+        <v>-0.13131313131313119</v>
       </c>
       <c r="E47">
         <v>0.96997732400000003</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>0.66032564841498564</v>
+        <v>-2.1419308357348704E-3</v>
       </c>
       <c r="C48">
-        <v>2.2044088176352412E-2</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="E48">
         <v>0.976169862</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.72564985590778097</v>
+        <v>5.6863112391930835E-2</v>
       </c>
       <c r="C49">
-        <v>5.0100200400801737E-2</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="E49">
         <v>0.98877757200000005</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.75659221902017293</v>
+        <v>0.11614726224783861</v>
       </c>
       <c r="C50">
-        <v>7.8156312625250524E-2</v>
+        <v>-7.0707070707070635E-2</v>
       </c>
       <c r="E50">
         <v>1.0013028239999999</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.77369020172910663</v>
+        <v>0.19069164265129684</v>
       </c>
       <c r="C51">
-        <v>0.1022044088176351</v>
+        <v>-5.0505050505050497E-2</v>
       </c>
       <c r="E51">
         <v>1.0010554519999999</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.78820605187319881</v>
+        <v>0.27962247838616716</v>
       </c>
       <c r="C52">
-        <v>0.13026052104208441</v>
+        <v>-3.030303030303038E-2</v>
       </c>
       <c r="E52">
         <v>1.0038837350000001</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.8014020172910663</v>
+        <v>0.42598991354466859</v>
       </c>
       <c r="C53">
-        <v>0.1583166332665332</v>
+        <v>-1.010101010101006E-2</v>
       </c>
       <c r="E53">
         <v>1.003619872</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.81227233429394807</v>
+        <v>0.52559077809798271</v>
       </c>
       <c r="C54">
-        <v>0.18637274549098201</v>
+        <v>1.010101010101006E-2</v>
       </c>
       <c r="E54">
         <v>1.0065388580000001</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.82238328530259375</v>
+        <v>0.61280547550432274</v>
       </c>
       <c r="C55">
-        <v>0.210420841683367</v>
+        <v>3.0303030303030189E-2</v>
       </c>
       <c r="E55">
         <v>1.0062667489999999</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.83186743515850148</v>
+        <v>0.68062103746397695</v>
       </c>
       <c r="C56">
-        <v>0.2384769539078154</v>
+        <v>5.0505050505050317E-2</v>
       </c>
       <c r="E56">
         <v>1.009103278</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.84024927953890494</v>
+        <v>0.74220461095100865</v>
       </c>
       <c r="C57">
-        <v>0.26653306613226457</v>
+        <v>7.0707070707070635E-2</v>
       </c>
       <c r="E57">
         <v>1.008872397</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.84869740634005764</v>
+        <v>0.76547406340057644</v>
       </c>
       <c r="C58">
-        <v>0.29058116232464931</v>
+        <v>9.0909090909091134E-2</v>
       </c>
       <c r="E58">
         <v>1.0086085339999999</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.85627233429394822</v>
+        <v>0.78274927953890483</v>
       </c>
       <c r="C59">
-        <v>0.3186372745490979</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="E59">
         <v>1.0083446709999999</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.86382420749279543</v>
+        <v>0.7975000000000001</v>
       </c>
       <c r="C60">
-        <v>0.34669338677354722</v>
+        <v>0.13131313131313119</v>
       </c>
       <c r="H60">
         <v>-5.70313E-2</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.87095533141210368</v>
+        <v>0.81628386167146971</v>
       </c>
       <c r="C61">
-        <v>0.37474949899799598</v>
+        <v>0.15151515151515171</v>
       </c>
       <c r="H61">
         <v>-5.6545999999999999E-2</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.87830259365994245</v>
+        <v>0.82782564841498552</v>
       </c>
       <c r="C62">
-        <v>0.39879759519038072</v>
+        <v>0.17171717171717149</v>
       </c>
       <c r="H62">
         <v>-5.6041599999999997E-2</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>0.8852118155619596</v>
+        <v>0.83896109510086458</v>
       </c>
       <c r="C63">
-        <v>0.42685370741482992</v>
+        <v>0.19191919191919179</v>
       </c>
       <c r="H63">
         <v>-5.5537799999999998E-2</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>0.89280835734870323</v>
+        <v>0.85394524495677238</v>
       </c>
       <c r="C64">
-        <v>0.45490981963927868</v>
+        <v>0.21212121212121229</v>
       </c>
       <c r="H64">
         <v>-5.5022099999999997E-2</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>0.89923342939481266</v>
+        <v>0.863350144092219</v>
       </c>
       <c r="C65">
-        <v>0.47895791583166319</v>
+        <v>0.23232323232323199</v>
       </c>
       <c r="H65">
         <v>-5.45041E-2</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>0.90634726224783857</v>
+        <v>0.87223487031700286</v>
       </c>
       <c r="C66">
-        <v>0.50701402805611218</v>
+        <v>0.25252525252525232</v>
       </c>
       <c r="H66">
         <v>-5.3986800000000001E-2</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>0.91223342939481278</v>
+        <v>0.88033573487031702</v>
       </c>
       <c r="C67">
-        <v>0.5350701402805611</v>
+        <v>0.27272727272727237</v>
       </c>
       <c r="H67">
         <v>-5.3469900000000001E-2</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>0.91863976945244952</v>
+        <v>0.89250288184438042</v>
       </c>
       <c r="C68">
-        <v>0.56312625250500992</v>
+        <v>0.29292929292929321</v>
       </c>
       <c r="H68">
         <v>-5.2934099999999998E-2</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>0.92451873198847256</v>
+        <v>0.90018731988472622</v>
       </c>
       <c r="C69">
-        <v>0.5871743486973946</v>
+        <v>0.31313131313131332</v>
       </c>
       <c r="H69">
         <v>-5.2396699999999997E-2</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>0.93098847262247841</v>
+        <v>0.90696685878962524</v>
       </c>
       <c r="C70">
-        <v>0.61523046092184352</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="H70">
         <v>-5.1858599999999998E-2</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>0.93736887608069164</v>
+        <v>0.91414985590778097</v>
       </c>
       <c r="C71">
-        <v>0.64328657314629256</v>
+        <v>0.35353535353535331</v>
       </c>
       <c r="H71">
         <v>-5.1312000000000003E-2</v>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>0.94388184438040346</v>
+        <v>0.92458501440922192</v>
       </c>
       <c r="C72">
-        <v>0.66733466933867747</v>
+        <v>0.37373737373737348</v>
       </c>
       <c r="H72">
         <v>-5.07552E-2</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>0.95020317002881849</v>
+        <v>0.9318357348703169</v>
       </c>
       <c r="C73">
-        <v>0.69539078156312606</v>
+        <v>0.39393939393939409</v>
       </c>
       <c r="H73">
         <v>-5.01874E-2</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>0.95620461095100862</v>
+        <v>0.9390619596541786</v>
       </c>
       <c r="C74">
-        <v>0.72344689378757532</v>
+        <v>0.41414141414141448</v>
       </c>
       <c r="H74">
         <v>-4.9605999999999997E-2</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>0.96184582132564833</v>
+        <v>0.94637319884726223</v>
       </c>
       <c r="C75">
-        <v>0.75150300601202391</v>
+        <v>0.43434343434343442</v>
       </c>
       <c r="H75">
         <v>-4.9023299999999999E-2</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>0.96711959654178681</v>
+        <v>0.95598126801152739</v>
       </c>
       <c r="C76">
-        <v>0.77555110220440904</v>
+        <v>0.4545454545454547</v>
       </c>
       <c r="H76">
         <v>-4.8441100000000001E-2</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>0.97201873198847266</v>
+        <v>0.96163544668587897</v>
       </c>
       <c r="C77">
-        <v>0.80360721442885763</v>
+        <v>0.47474747474747497</v>
       </c>
       <c r="H77">
         <v>-4.78629E-2</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>0.97658069164265127</v>
+        <v>0.96722910662824202</v>
       </c>
       <c r="C78">
-        <v>0.83166332665330656</v>
+        <v>0.49494949494949508</v>
       </c>
       <c r="H78">
         <v>-4.7284800000000002E-2</v>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>0.98083141210374636</v>
+        <v>0.97432708933717582</v>
       </c>
       <c r="C79">
-        <v>0.85571142284569135</v>
+        <v>0.51515151515151525</v>
       </c>
       <c r="H79">
         <v>-4.6739599999999999E-2</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>0.98465706051873192</v>
+        <v>0.97867291066282414</v>
       </c>
       <c r="C80">
-        <v>0.88376753507014028</v>
+        <v>0.53535353535353536</v>
       </c>
       <c r="H80">
         <v>-4.6187899999999997E-2</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>0.98798847262247835</v>
+        <v>0.98305619596541782</v>
       </c>
       <c r="C81">
-        <v>0.9118236472945892</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H81">
         <v>-4.5587200000000001E-2</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>0.99081412103746402</v>
+        <v>0.98722334293948133</v>
       </c>
       <c r="C82">
-        <v>0.93587174348697399</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="H82">
         <v>-4.4986499999999999E-2</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>0.99320461095100865</v>
+        <v>0.9936210374639769</v>
       </c>
       <c r="C83">
-        <v>0.96392785571142292</v>
+        <v>0.59595959595959558</v>
       </c>
       <c r="H83">
         <v>-4.4388299999999999E-2</v>
@@ -2093,10 +2093,10 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>0.9952463976945245</v>
+        <v>0.99798703170028813</v>
       </c>
       <c r="C84">
-        <v>0.99198396793587151</v>
+        <v>0.61616161616161624</v>
       </c>
       <c r="H84">
         <v>-4.37957E-2</v>
@@ -2106,6 +2106,12 @@
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85">
+        <v>1.0019985590778098</v>
+      </c>
+      <c r="C85">
+        <v>0.63636363636363646</v>
+      </c>
       <c r="H85">
         <v>-4.3196499999999999E-2</v>
       </c>
@@ -2114,6 +2120,12 @@
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>1.0057190201729107</v>
+      </c>
+      <c r="C86">
+        <v>0.65656565656565657</v>
+      </c>
       <c r="H86">
         <v>-4.2597299999999998E-2</v>
       </c>
@@ -2122,6 +2134,12 @@
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>1.0107478386167146</v>
+      </c>
+      <c r="C87">
+        <v>0.67676767676767691</v>
+      </c>
       <c r="H87">
         <v>-4.1983600000000003E-2</v>
       </c>
@@ -2130,6 +2148,12 @@
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>1.0136930835734872</v>
+      </c>
+      <c r="C88">
+        <v>0.69696969696969702</v>
+      </c>
       <c r="H88">
         <v>-4.1360099999999997E-2</v>
       </c>
@@ -2138,6 +2162,12 @@
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>1.0162103746397695</v>
+      </c>
+      <c r="C89">
+        <v>0.71717171717171713</v>
+      </c>
       <c r="H89">
         <v>-4.0736500000000002E-2</v>
       </c>
@@ -2146,6 +2176,12 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>1.019456772334294</v>
+      </c>
+      <c r="C90">
+        <v>0.73737373737373757</v>
+      </c>
       <c r="H90">
         <v>-4.0105099999999998E-2</v>
       </c>
@@ -2154,6 +2190,12 @@
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>1.0211412103746398</v>
+      </c>
+      <c r="C91">
+        <v>0.75757575757575735</v>
+      </c>
       <c r="H91">
         <v>-3.94592E-2</v>
       </c>
@@ -2162,6 +2204,12 @@
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>1.0225100864553314</v>
+      </c>
+      <c r="C92">
+        <v>0.7777777777777779</v>
+      </c>
       <c r="H92">
         <v>-3.8813300000000002E-2</v>
       </c>
@@ -2170,6 +2218,12 @@
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>1.0235086455331412</v>
+      </c>
+      <c r="C93">
+        <v>0.79797979797979801</v>
+      </c>
       <c r="H93">
         <v>-3.8175800000000003E-2</v>
       </c>
@@ -2178,6 +2232,12 @@
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>1.0244769452449567</v>
+      </c>
+      <c r="C94">
+        <v>0.81818181818181812</v>
+      </c>
       <c r="H94">
         <v>-3.7557599999999997E-2</v>
       </c>
@@ -2186,6 +2246,12 @@
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>1.0247536023054755</v>
+      </c>
+      <c r="C95">
+        <v>0.83838383838383823</v>
+      </c>
       <c r="H95">
         <v>-3.69465E-2</v>
       </c>
@@ -2194,6 +2260,12 @@
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>1.0247752161383286</v>
+      </c>
+      <c r="C96">
+        <v>0.85858585858585879</v>
+      </c>
       <c r="H96">
         <v>-3.6335399999999997E-2</v>
       </c>
@@ -2201,7 +2273,13 @@
         <v>-0.652114976318798</v>
       </c>
     </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>1.0246268011527377</v>
+      </c>
+      <c r="C97">
+        <v>0.8787878787878789</v>
+      </c>
       <c r="H97">
         <v>-3.5730100000000001E-2</v>
       </c>
@@ -2209,7 +2287,13 @@
         <v>-0.6480646741793239</v>
       </c>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>1.0240115273775217</v>
+      </c>
+      <c r="C98">
+        <v>0.89898989898989901</v>
+      </c>
       <c r="H98">
         <v>-3.5114399999999997E-2</v>
       </c>
@@ -2217,7 +2301,13 @@
         <v>-0.64401437203984968</v>
       </c>
     </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99">
+        <v>1.0234121037463977</v>
+      </c>
+      <c r="C99">
+        <v>0.91919191919191912</v>
+      </c>
       <c r="H99">
         <v>-3.4485399999999999E-2</v>
       </c>
@@ -2225,7 +2315,13 @@
         <v>-0.63996406990037558</v>
       </c>
     </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100">
+        <v>1.0226974063400576</v>
+      </c>
+      <c r="C100">
+        <v>0.93939393939393923</v>
+      </c>
       <c r="H100">
         <v>-3.3856400000000002E-2</v>
       </c>
@@ -2233,7 +2329,13 @@
         <v>-0.63591376776090147</v>
       </c>
     </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B101">
+        <v>1.0218631123919308</v>
+      </c>
+      <c r="C101">
+        <v>0.95959595959596011</v>
+      </c>
       <c r="H101">
         <v>-3.3227399999999997E-2</v>
       </c>
@@ -2241,7 +2343,13 @@
         <v>-0.6318689095759159</v>
       </c>
     </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102">
+        <v>1.0203890489913545</v>
+      </c>
+      <c r="C102">
+        <v>0.97979797979797989</v>
+      </c>
       <c r="H102">
         <v>-3.2604500000000002E-2</v>
       </c>
@@ -2249,7 +2357,13 @@
         <v>-0.6278186074364418</v>
       </c>
     </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103">
+        <v>1.0193011527377522</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
       <c r="H103">
         <v>-3.1967299999999997E-2</v>
       </c>
@@ -2257,7 +2371,7 @@
         <v>-0.6237683052969677</v>
       </c>
     </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H104">
         <v>-3.1323299999999998E-2</v>
       </c>
@@ -2265,7 +2379,7 @@
         <v>-0.61971800315749359</v>
       </c>
     </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H105">
         <v>-3.06792E-2</v>
       </c>
@@ -2273,7 +2387,7 @@
         <v>-0.61566770101801949</v>
       </c>
     </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H106">
         <v>-3.0035099999999999E-2</v>
       </c>
@@ -2281,7 +2395,7 @@
         <v>-0.61162284283303392</v>
       </c>
     </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H107">
         <v>-2.93911E-2</v>
       </c>
@@ -2289,7 +2403,7 @@
         <v>-0.60757254069355981</v>
       </c>
     </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H108">
         <v>-2.87456E-2</v>
       </c>
@@ -2297,7 +2411,7 @@
         <v>-0.60352223855408571</v>
       </c>
     </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H109">
         <v>-2.8086E-2</v>
       </c>
@@ -2305,7 +2419,7 @@
         <v>-0.59947193641461149</v>
       </c>
     </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H110">
         <v>-2.7426200000000001E-2</v>
       </c>
@@ -2313,7 +2427,7 @@
         <v>-0.59542163427513739</v>
       </c>
     </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H111">
         <v>-2.67663E-2</v>
       </c>
@@ -2321,7 +2435,7 @@
         <v>-0.59137677609015182</v>
       </c>
     </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H112">
         <v>-2.60916E-2</v>
       </c>
@@ -5476,51 +5590,51 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>5</v>
-      </c>
       <c r="L3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>-9.4163832853025931E-2</v>
+        <v>-0.13976945244956773</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -5546,10 +5660,10 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>-0.1210770893371758</v>
+        <v>-0.14002838616714697</v>
       </c>
       <c r="C5">
-        <v>-0.98396793587174336</v>
+        <v>-0.97979797979797989</v>
       </c>
       <c r="E5">
         <v>-0.156104723</v>
@@ -5572,10 +5686,10 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>-0.13257953890489912</v>
+        <v>-0.1564322766570605</v>
       </c>
       <c r="C6">
-        <v>-0.97194388777555107</v>
+        <v>-0.95959595959595956</v>
       </c>
       <c r="E6">
         <v>-0.14662503099999999</v>
@@ -5598,10 +5712,10 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>-0.14007694524495676</v>
+        <v>-0.16336743515850144</v>
       </c>
       <c r="C7">
-        <v>-0.95991983967935868</v>
+        <v>-0.93939393939393945</v>
       </c>
       <c r="E7">
         <v>-0.146707751</v>
@@ -5624,10 +5738,10 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>-0.14404755043227666</v>
+        <v>-0.16696685878962536</v>
       </c>
       <c r="C8">
-        <v>-0.94388777555110226</v>
+        <v>-0.91919191919191912</v>
       </c>
       <c r="E8">
         <v>-0.12769873400000001</v>
@@ -5650,10 +5764,10 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>-0.14487031700288186</v>
+        <v>-0.16727809798270893</v>
       </c>
       <c r="C9">
-        <v>-0.93186372745490986</v>
+        <v>-0.89898989898989901</v>
       </c>
       <c r="E9">
         <v>-0.124567789</v>
@@ -5676,10 +5790,10 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>-0.14454610951008645</v>
+        <v>-0.16717867435158501</v>
       </c>
       <c r="C10">
-        <v>-0.91583166332665333</v>
+        <v>-0.8787878787878789</v>
       </c>
       <c r="E10">
         <v>-0.13097444</v>
@@ -5702,10 +5816,10 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>-0.14399135446685879</v>
+        <v>-0.16592507204610951</v>
       </c>
       <c r="C11">
-        <v>-0.90380761523046094</v>
+        <v>-0.85858585858585856</v>
       </c>
       <c r="E11">
         <v>-0.12147820300000001</v>
@@ -5728,10 +5842,10 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>-0.1419621037463977</v>
+        <v>-0.16369164265129685</v>
       </c>
       <c r="C12">
-        <v>-0.89178356713426854</v>
+        <v>-0.83838383838383845</v>
       </c>
       <c r="E12">
         <v>-0.115183224</v>
@@ -5754,10 +5868,10 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>-0.13971959654178676</v>
+        <v>-0.16198270893371758</v>
       </c>
       <c r="C13">
-        <v>-0.87575150300601201</v>
+        <v>-0.81818181818181823</v>
       </c>
       <c r="E13">
         <v>-0.11208536700000001</v>
@@ -5780,10 +5894,10 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>-0.13722953890489914</v>
+        <v>-0.16028097982708933</v>
       </c>
       <c r="C14">
-        <v>-0.86372745490981961</v>
+        <v>-0.79797979797979801</v>
       </c>
       <c r="E14">
         <v>-0.102609811</v>
@@ -5806,10 +5920,10 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>-0.13379322766570606</v>
+        <v>-0.15812968299711816</v>
       </c>
       <c r="C15">
-        <v>-0.85170340681362722</v>
+        <v>-0.77777777777777779</v>
       </c>
       <c r="E15">
         <v>-9.9491273000000005E-2</v>
@@ -5832,10 +5946,10 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>-0.12700028818443804</v>
+        <v>-0.15480259365994237</v>
       </c>
       <c r="C16">
-        <v>-0.8236472945891784</v>
+        <v>-0.75757575757575757</v>
       </c>
       <c r="E16">
         <v>-8.0440896999999997E-2</v>
@@ -5858,10 +5972,10 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>-0.11842046109510088</v>
+        <v>-0.15204755043227666</v>
       </c>
       <c r="C17">
-        <v>-0.81162324649298589</v>
+        <v>-0.73737373737373746</v>
       </c>
       <c r="E17">
         <v>-6.1361567999999998E-2</v>
@@ -5884,10 +5998,10 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>-0.10992219020172911</v>
+        <v>-0.14913400576368877</v>
       </c>
       <c r="C18">
-        <v>-0.78356713426853708</v>
+        <v>-0.71717171717171713</v>
       </c>
       <c r="E18">
         <v>-5.5066588999999999E-2</v>
@@ -5910,10 +6024,10 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>-0.10043904899135447</v>
+        <v>-0.14605763688760809</v>
       </c>
       <c r="C19">
-        <v>-0.75551102204408815</v>
+        <v>-0.69696969696969702</v>
       </c>
       <c r="E19">
         <v>-4.2373231999999997E-2</v>
@@ -5936,10 +6050,10 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>-9.1661239193083582E-2</v>
+        <v>-0.14094538904899137</v>
       </c>
       <c r="C20">
-        <v>-0.73146292585170325</v>
+        <v>-0.6767676767676768</v>
       </c>
       <c r="E20">
         <v>-2.6515840999999998E-2</v>
@@ -5962,10 +6076,10 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>-8.2707925072046107E-2</v>
+        <v>-0.13762190201729108</v>
       </c>
       <c r="C21">
-        <v>-0.70340681362725455</v>
+        <v>-0.65656565656565657</v>
       </c>
       <c r="E21">
         <v>-7.4447849999999998E-3</v>
@@ -5988,10 +6102,10 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>-7.3517146974063391E-2</v>
+        <v>-0.1341014409221902</v>
       </c>
       <c r="C22">
-        <v>-0.67535070140280551</v>
+        <v>-0.63636363636363646</v>
       </c>
       <c r="E22">
         <v>2.4340309000000001E-2</v>
@@ -6014,10 +6128,10 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>-6.3450432276657059E-2</v>
+        <v>-0.12831037463976944</v>
       </c>
       <c r="C23">
-        <v>-0.64729458917835681</v>
+        <v>-0.61616161616161613</v>
       </c>
       <c r="E23">
         <v>3.3828273999999998E-2</v>
@@ -6040,10 +6154,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>-5.3807925072046112E-2</v>
+        <v>-0.12382204610951009</v>
       </c>
       <c r="C24">
-        <v>-0.6232464929859719</v>
+        <v>-0.59595959595959602</v>
       </c>
       <c r="E24">
         <v>4.9689800999999999E-2</v>
@@ -6066,10 +6180,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>-4.4768731988472622E-2</v>
+        <v>-0.11948011527377522</v>
       </c>
       <c r="C25">
-        <v>-0.59519038076152309</v>
+        <v>-0.5757575757575758</v>
       </c>
       <c r="E25">
         <v>7.5117876E-2</v>
@@ -6092,10 +6206,10 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>-3.6135446685878959E-2</v>
+        <v>-0.11470446685878963</v>
       </c>
       <c r="C26">
-        <v>-0.56713426853707416</v>
+        <v>-0.55555555555555558</v>
       </c>
       <c r="E26">
         <v>0.10375548</v>
@@ -6118,10 +6232,10 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>-2.7814985590778097E-2</v>
+        <v>-0.10719207492795389</v>
       </c>
       <c r="C27">
-        <v>-0.54308617234468937</v>
+        <v>-0.53535353535353536</v>
       </c>
       <c r="E27">
         <v>0.14194308899999999</v>
@@ -6144,10 +6258,10 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>-1.9210374639769455E-2</v>
+        <v>-0.10197622478386167</v>
       </c>
       <c r="C28">
-        <v>-0.51503006012024044</v>
+        <v>-0.51515151515151525</v>
       </c>
       <c r="E28">
         <v>0.18331541100000001</v>
@@ -6170,10 +6284,10 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>-1.0728890489913545E-2</v>
+        <v>-9.6716282420749283E-2</v>
       </c>
       <c r="C29">
-        <v>-0.48697394789579163</v>
+        <v>-0.49494949494949497</v>
       </c>
       <c r="E29">
         <v>0.21194474299999999</v>
@@ -6196,10 +6310,10 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>-2.0404034582132565E-3</v>
+        <v>-9.1372334293948129E-2</v>
       </c>
       <c r="C30">
-        <v>-0.45891783567134259</v>
+        <v>-0.47474747474747492</v>
       </c>
       <c r="E30">
         <v>0.24695177400000001</v>
@@ -6222,10 +6336,10 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>6.5788760806916426E-3</v>
+        <v>-8.2589481268011536E-2</v>
       </c>
       <c r="C31">
-        <v>-0.4348697394789578</v>
+        <v>-0.45454545454545442</v>
       </c>
       <c r="E31">
         <v>0.27558524299999998</v>
@@ -6248,10 +6362,10 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>1.4909221902017291E-2</v>
+        <v>-7.6694380403458218E-2</v>
       </c>
       <c r="C32">
-        <v>-0.40681362725450898</v>
+        <v>-0.43434343434343442</v>
       </c>
       <c r="E32">
         <v>0.30421871099999998</v>
@@ -6268,10 +6382,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>2.3773631123919305E-2</v>
+        <v>-7.0008357348703171E-2</v>
       </c>
       <c r="C33">
-        <v>-0.37875751503006022</v>
+        <v>-0.41414141414141431</v>
       </c>
       <c r="E33">
         <v>0.351952188</v>
@@ -6288,10 +6402,10 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>3.2429106628242076E-2</v>
+        <v>-5.9181844380403463E-2</v>
       </c>
       <c r="C34">
-        <v>-0.35470941883767543</v>
+        <v>-0.39393939393939392</v>
       </c>
       <c r="E34">
         <v>0.39014806800000001</v>
@@ -6308,10 +6422,10 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>4.3319596541786742E-2</v>
+        <v>-5.1100720461095102E-2</v>
       </c>
       <c r="C35">
-        <v>-0.32665330661322639</v>
+        <v>-0.37373737373737381</v>
       </c>
       <c r="E35">
         <v>0.42195797800000001</v>
@@ -6328,10 +6442,10 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>5.6291642651296832E-2</v>
+        <v>-4.1628097982708938E-2</v>
       </c>
       <c r="C36">
-        <v>-0.29859719438877758</v>
+        <v>-0.35353535353535342</v>
       </c>
       <c r="E36">
         <v>0.46333443600000002</v>
@@ -6348,10 +6462,10 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>7.2370028818443802E-2</v>
+        <v>-3.1697406340057639E-2</v>
       </c>
       <c r="C37">
-        <v>-0.27054108216432871</v>
+        <v>-0.33333333333333331</v>
       </c>
       <c r="E37">
         <v>0.501513773</v>
@@ -6368,10 +6482,10 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>9.4173054755043228E-2</v>
+        <v>-1.4497694524495678E-2</v>
       </c>
       <c r="C38">
-        <v>-0.24649298597194369</v>
+        <v>-0.31313131313131332</v>
       </c>
       <c r="E38">
         <v>0.56836380200000003</v>
@@ -6388,10 +6502,10 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>0.12328703170028818</v>
+        <v>-8.5811959654178685E-4</v>
       </c>
       <c r="C39">
-        <v>-0.2184368737474951</v>
+        <v>-0.29292929292929287</v>
       </c>
       <c r="E39">
         <v>0.62565141899999999</v>
@@ -6408,10 +6522,10 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>0.16019740634005764</v>
+        <v>1.4438616714697407E-2</v>
       </c>
       <c r="C40">
-        <v>-0.190380761523046</v>
+        <v>-0.27272727272727282</v>
       </c>
       <c r="E40">
         <v>0.651112582</v>
@@ -6428,10 +6542,10 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>0.20422910662824209</v>
+        <v>3.2214697406340059E-2</v>
       </c>
       <c r="C41">
-        <v>-0.16633266533066141</v>
+        <v>-0.25252525252525237</v>
       </c>
       <c r="E41">
         <v>0.69566134499999999</v>
@@ -6448,10 +6562,10 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>0.25514841498559077</v>
+        <v>6.3818587896253609E-2</v>
       </c>
       <c r="C42">
-        <v>-0.13827655310621231</v>
+        <v>-0.23232323232323229</v>
       </c>
       <c r="E42">
         <v>0.74976838400000001</v>
@@ -6468,10 +6582,10 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>0.31270317002881842</v>
+        <v>8.7129106628242067E-2</v>
       </c>
       <c r="C43">
-        <v>-0.1102204408817635</v>
+        <v>-0.21212121212121199</v>
       </c>
       <c r="E43">
         <v>0.79750186099999998</v>
@@ -6488,10 +6602,10 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>0.37495965417867433</v>
+        <v>0.11320028818443804</v>
       </c>
       <c r="C44">
-        <v>-8.2164328657314586E-2</v>
+        <v>-0.19191919191919191</v>
       </c>
       <c r="E44">
         <v>0.835685334</v>
@@ -6508,10 +6622,10 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>0.43795244956772339</v>
+        <v>0.14216815561959653</v>
       </c>
       <c r="C45">
-        <v>-5.8116232464929862E-2</v>
+        <v>-0.17171717171717171</v>
       </c>
       <c r="E45">
         <v>0.88021755300000004</v>
@@ -6528,10 +6642,10 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>0.50411527377521614</v>
+        <v>0.18985446685878959</v>
       </c>
       <c r="C46">
-        <v>-3.0060120240481089E-2</v>
+        <v>-0.15151515151515149</v>
       </c>
       <c r="E46">
         <v>0.90564976399999997</v>
@@ -6548,10 +6662,10 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>0.57286743515850147</v>
+        <v>0.22470893371757927</v>
       </c>
       <c r="C47">
-        <v>-2.0040080160317491E-3</v>
+        <v>-0.13131313131313119</v>
       </c>
       <c r="E47">
         <v>0.93106956699999999</v>
@@ -6568,10 +6682,10 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>0.63128097982708931</v>
+        <v>0.2604971181556196</v>
       </c>
       <c r="C48">
-        <v>2.2044088176352412E-2</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="E48">
         <v>0.94056994000000005</v>
@@ -6588,10 +6702,10 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.6859337175792507</v>
+        <v>0.31923198847262246</v>
       </c>
       <c r="C49">
-        <v>5.0100200400801737E-2</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="E49">
         <v>0.95962031599999997</v>
@@ -6608,10 +6722,10 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.72972622478386173</v>
+        <v>0.36149855907780981</v>
       </c>
       <c r="C50">
-        <v>7.8156312625250524E-2</v>
+        <v>-7.0707070707070635E-2</v>
       </c>
       <c r="E50">
         <v>0.97864587599999997</v>
@@ -6628,10 +6742,10 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.76376512968299715</v>
+        <v>0.40483285302593663</v>
       </c>
       <c r="C51">
-        <v>0.1022044088176351</v>
+        <v>-5.0505050505050497E-2</v>
       </c>
       <c r="E51">
         <v>0.98811729699999995</v>
@@ -6648,10 +6762,10 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.7897622478386167</v>
+        <v>0.44962680115273773</v>
       </c>
       <c r="C52">
-        <v>0.13026052104208441</v>
+        <v>-3.030303030303038E-2</v>
       </c>
       <c r="E52">
         <v>0.997592853</v>
@@ -6668,10 +6782,10 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.80793227665706058</v>
+        <v>0.52126224783861663</v>
       </c>
       <c r="C53">
-        <v>0.1583166332665332</v>
+        <v>-1.010101010101006E-2</v>
       </c>
       <c r="E53">
         <v>1.007056001</v>
@@ -6688,10 +6802,10 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.82019308357348708</v>
+        <v>0.56671181556195971</v>
       </c>
       <c r="C54">
-        <v>0.18637274549098201</v>
+        <v>1.010101010101006E-2</v>
       </c>
       <c r="E54">
         <v>1.0069526019999999</v>
@@ -6708,10 +6822,10 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.82993371757925083</v>
+        <v>0.61395533141210368</v>
       </c>
       <c r="C55">
-        <v>0.210420841683367</v>
+        <v>3.0303030303030189E-2</v>
       </c>
       <c r="E55">
         <v>1.010021507</v>
@@ -6728,10 +6842,10 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.83856195965417868</v>
+        <v>0.65656628242074921</v>
       </c>
       <c r="C56">
-        <v>0.2384769539078154</v>
+        <v>5.0505050505050317E-2</v>
       </c>
       <c r="E56">
         <v>1.009889155</v>
@@ -6748,10 +6862,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.84628962536023067</v>
+        <v>0.71378386167146968</v>
       </c>
       <c r="C57">
-        <v>0.26653306613226457</v>
+        <v>7.0707070707070635E-2</v>
       </c>
       <c r="E57">
         <v>1.0129042930000001</v>
@@ -6768,10 +6882,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.85357348703170033</v>
+        <v>0.74716858789625351</v>
       </c>
       <c r="C58">
-        <v>0.29058116232464931</v>
+        <v>9.0909090909091134E-2</v>
       </c>
       <c r="E58">
         <v>1.0127802130000001</v>
@@ -6788,10 +6902,10 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.86065561959654169</v>
+        <v>0.7748659942363112</v>
       </c>
       <c r="C59">
-        <v>0.3186372745490979</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="E59">
         <v>1.018971793</v>
@@ -6808,10 +6922,10 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.86743948126801163</v>
+        <v>0.79769452449567724</v>
       </c>
       <c r="C60">
-        <v>0.34669338677354722</v>
+        <v>0.13131313131313119</v>
       </c>
       <c r="E60">
         <v>1.015675407</v>
@@ -6828,10 +6942,10 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.87448559077809807</v>
+        <v>0.82489481268011522</v>
       </c>
       <c r="C61">
-        <v>0.37474949899799598</v>
+        <v>0.15151515151515171</v>
       </c>
       <c r="E61">
         <v>1.0123335259999999</v>
@@ -6848,10 +6962,10 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.88108213256484147</v>
+        <v>0.83881123919308354</v>
       </c>
       <c r="C62">
-        <v>0.39879759519038072</v>
+        <v>0.17171717171717149</v>
       </c>
       <c r="E62">
         <v>1.008946149</v>
@@ -6868,10 +6982,10 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>0.88737175792507206</v>
+        <v>0.85064409221902015</v>
       </c>
       <c r="C63">
-        <v>0.42685370741482992</v>
+        <v>0.19191919191919179</v>
       </c>
       <c r="H63">
         <v>-0.113125</v>
@@ -6882,10 +6996,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>0.89357348703170025</v>
+        <v>0.86597550432276649</v>
       </c>
       <c r="C64">
-        <v>0.45490981963927868</v>
+        <v>0.21212121212121229</v>
       </c>
       <c r="H64">
         <v>-0.111664</v>
@@ -6896,10 +7010,10 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>0.8998904899135447</v>
+        <v>0.8754582132564841</v>
       </c>
       <c r="C65">
-        <v>0.47895791583166319</v>
+        <v>0.23232323232323199</v>
       </c>
       <c r="H65">
         <v>-0.11020000000000001</v>
@@ -6910,10 +7024,10 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>0.90628674351585015</v>
+        <v>0.88452161383285299</v>
       </c>
       <c r="C66">
-        <v>0.50701402805611218</v>
+        <v>0.25252525252525232</v>
       </c>
       <c r="H66">
         <v>-0.108737</v>
@@ -6924,10 +7038,10 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>0.91251296829971185</v>
+        <v>0.89242651296829978</v>
       </c>
       <c r="C67">
-        <v>0.5350701402805611</v>
+        <v>0.27272727272727237</v>
       </c>
       <c r="H67">
         <v>-0.10727100000000001</v>
@@ -6938,10 +7052,10 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>0.91862968299711811</v>
+        <v>0.90463544668587892</v>
       </c>
       <c r="C68">
-        <v>0.56312625250500992</v>
+        <v>0.29292929292929321</v>
       </c>
       <c r="H68">
         <v>-0.10580299999999999</v>
@@ -6952,10 +7066,10 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>0.92463544668587894</v>
+        <v>0.91217146974063401</v>
       </c>
       <c r="C69">
-        <v>0.5871743486973946</v>
+        <v>0.31313131313131332</v>
       </c>
       <c r="H69">
         <v>-0.104336</v>
@@ -6966,10 +7080,10 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>0.93063688760806906</v>
+        <v>0.91927233429394817</v>
       </c>
       <c r="C70">
-        <v>0.61523046092184352</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="H70">
         <v>-0.10285999999999999</v>
@@ -6980,10 +7094,10 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>0.93672046109510076</v>
+        <v>0.92683861671469736</v>
       </c>
       <c r="C71">
-        <v>0.64328657314629256</v>
+        <v>0.35353535353535331</v>
       </c>
       <c r="H71">
         <v>-0.101383</v>
@@ -6994,10 +7108,10 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>0.94286887608069159</v>
+        <v>0.93660951008645521</v>
       </c>
       <c r="C72">
-        <v>0.66733466933867747</v>
+        <v>0.37373737373737348</v>
       </c>
       <c r="H72">
         <v>-9.9901400000000001E-2</v>
@@ -7008,10 +7122,10 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>0.94895821325648411</v>
+        <v>0.94306916426512966</v>
       </c>
       <c r="C73">
-        <v>0.69539078156312606</v>
+        <v>0.39393939393939409</v>
       </c>
       <c r="H73">
         <v>-9.8420999999999995E-2</v>
@@ -7022,10 +7136,10 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>0.95478818443804037</v>
+        <v>0.94915850144092218</v>
       </c>
       <c r="C74">
-        <v>0.72344689378757532</v>
+        <v>0.41414141414141448</v>
       </c>
       <c r="H74">
         <v>-9.6947099999999994E-2</v>
@@ -7036,10 +7150,10 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>0.96016714697406336</v>
+        <v>0.95514841498559089</v>
       </c>
       <c r="C75">
-        <v>0.75150300601202391</v>
+        <v>0.43434343434343442</v>
       </c>
       <c r="H75">
         <v>-9.5473199999999994E-2</v>
@@ -7050,10 +7164,10 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>0.96540778097982716</v>
+        <v>0.96363832853025932</v>
       </c>
       <c r="C76">
-        <v>0.77555110220440904</v>
+        <v>0.4545454545454547</v>
       </c>
       <c r="H76">
         <v>-9.3965199999999999E-2</v>
@@ -7064,10 +7178,10 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>0.9702968299711815</v>
+        <v>0.96910806916426517</v>
       </c>
       <c r="C77">
-        <v>0.80360721442885763</v>
+        <v>0.47474747474747497</v>
       </c>
       <c r="H77">
         <v>-9.2446700000000007E-2</v>
@@ -7078,10 +7192,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>0.97482132564841495</v>
+        <v>0.97432564841498559</v>
       </c>
       <c r="C78">
-        <v>0.83166332665330656</v>
+        <v>0.49494949494949508</v>
       </c>
       <c r="H78">
         <v>-9.0934100000000004E-2</v>
@@ -7092,10 +7206,10 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>0.97896541786743518</v>
+        <v>0.98153602305475507</v>
       </c>
       <c r="C79">
-        <v>0.85571142284569135</v>
+        <v>0.51515151515151525</v>
       </c>
       <c r="H79">
         <v>-8.9424299999999998E-2</v>
@@ -7106,10 +7220,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>0.98268587896253612</v>
+        <v>0.98612391930835741</v>
       </c>
       <c r="C80">
-        <v>0.88376753507014028</v>
+        <v>0.53535353535353536</v>
       </c>
       <c r="H80">
         <v>-8.7924699999999995E-2</v>
@@ -7120,10 +7234,10 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>0.98589625360230548</v>
+        <v>0.99067291066282426</v>
       </c>
       <c r="C81">
-        <v>0.9118236472945892</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H81">
         <v>-8.6441599999999993E-2</v>
@@ -7134,10 +7248,10 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>0.98861095100864549</v>
+        <v>0.99503746397694526</v>
       </c>
       <c r="C82">
-        <v>0.93587174348697399</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="H82">
         <v>-8.4958400000000003E-2</v>
@@ -7148,10 +7262,10 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>0.99088040345821338</v>
+        <v>1.0010907780979825</v>
       </c>
       <c r="C83">
-        <v>0.96392785571142292</v>
+        <v>0.59595959595959558</v>
       </c>
       <c r="H83">
         <v>-8.3475199999999999E-2</v>
@@ -7162,10 +7276,10 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>0.99279827089337169</v>
+        <v>1.0048703170028819</v>
       </c>
       <c r="C84">
-        <v>0.99198396793587151</v>
+        <v>0.61616161616161624</v>
       </c>
       <c r="H84">
         <v>-8.1941899999999998E-2</v>
@@ -7175,6 +7289,12 @@
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85">
+        <v>1.0084293948126801</v>
+      </c>
+      <c r="C85">
+        <v>0.63636363636363646</v>
+      </c>
       <c r="H85">
         <v>-8.0401700000000006E-2</v>
       </c>
@@ -7183,6 +7303,12 @@
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>1.0116873198847263</v>
+      </c>
+      <c r="C86">
+        <v>0.65656565656565657</v>
+      </c>
       <c r="H86">
         <v>-7.8879299999999999E-2</v>
       </c>
@@ -7191,6 +7317,12 @@
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>1.0158587896253601</v>
+      </c>
+      <c r="C87">
+        <v>0.67676767676767691</v>
+      </c>
       <c r="H87">
         <v>-7.7399800000000005E-2</v>
       </c>
@@ -7199,6 +7331,12 @@
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>1.0181757925072046</v>
+      </c>
+      <c r="C88">
+        <v>0.69696969696969702</v>
+      </c>
       <c r="H88">
         <v>-7.5924699999999998E-2</v>
       </c>
@@ -7207,6 +7345,12 @@
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>1.0201959654178674</v>
+      </c>
+      <c r="C89">
+        <v>0.71717171717171713</v>
+      </c>
       <c r="H89">
         <v>-7.4449600000000005E-2</v>
       </c>
@@ -7215,6 +7359,12 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>1.0226757925072045</v>
+      </c>
+      <c r="C90">
+        <v>0.73737373737373757</v>
+      </c>
       <c r="H90">
         <v>-7.2974600000000001E-2</v>
       </c>
@@ -7223,6 +7373,12 @@
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>1.02392795389049</v>
+      </c>
+      <c r="C91">
+        <v>0.75757575757575735</v>
+      </c>
       <c r="H91">
         <v>-7.1506600000000003E-2</v>
       </c>
@@ -7231,6 +7387,12 @@
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>1.0248876080691642</v>
+      </c>
+      <c r="C92">
+        <v>0.7777777777777779</v>
+      </c>
       <c r="H92">
         <v>-7.0054000000000005E-2</v>
       </c>
@@ -7239,6 +7401,12 @@
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>1.0255000000000001</v>
+      </c>
+      <c r="C93">
+        <v>0.79797979797979801</v>
+      </c>
       <c r="H93">
         <v>-6.8585099999999996E-2</v>
       </c>
@@ -7247,6 +7415,12 @@
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>1.0260115273775217</v>
+      </c>
+      <c r="C94">
+        <v>0.81818181818181812</v>
+      </c>
       <c r="H94">
         <v>-6.7104999999999998E-2</v>
       </c>
@@ -7255,6 +7429,12 @@
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>1.0260821325648415</v>
+      </c>
+      <c r="C95">
+        <v>0.83838383838383823</v>
+      </c>
       <c r="H95">
         <v>-6.5606800000000007E-2</v>
       </c>
@@ -7263,6 +7443,12 @@
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>1.0258962536023055</v>
+      </c>
+      <c r="C96">
+        <v>0.85858585858585879</v>
+      </c>
       <c r="H96">
         <v>-6.4108200000000004E-2</v>
       </c>
@@ -7270,7 +7456,13 @@
         <v>-0.69733790625510361</v>
       </c>
     </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>1.0254927953890489</v>
+      </c>
+      <c r="C97">
+        <v>0.8787878787878789</v>
+      </c>
       <c r="H97">
         <v>-6.25888E-2</v>
       </c>
@@ -7278,7 +7470,13 @@
         <v>-0.69328760411562962</v>
       </c>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>1.024577809798271</v>
+      </c>
+      <c r="C98">
+        <v>0.89898989898989901</v>
+      </c>
       <c r="H98">
         <v>-6.1060400000000001E-2</v>
       </c>
@@ -7286,7 +7484,13 @@
         <v>-0.68924274593064405</v>
       </c>
     </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99">
+        <v>1.0237780979827089</v>
+      </c>
+      <c r="C99">
+        <v>0.91919191919191912</v>
+      </c>
       <c r="H99">
         <v>-5.9528600000000001E-2</v>
       </c>
@@ -7294,7 +7498,13 @@
         <v>-0.68519244379116984</v>
       </c>
     </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100">
+        <v>1.0229005763688761</v>
+      </c>
+      <c r="C100">
+        <v>0.93939393939393923</v>
+      </c>
       <c r="H100">
         <v>-5.8042499999999997E-2</v>
       </c>
@@ -7302,7 +7512,13 @@
         <v>-0.68114214165169573</v>
       </c>
     </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B101">
+        <v>1.0220461095100863</v>
+      </c>
+      <c r="C101">
+        <v>0.95959595959596011</v>
+      </c>
       <c r="H101">
         <v>-5.6571200000000002E-2</v>
       </c>
@@ -7310,7 +7526,13 @@
         <v>-0.67709183951222174</v>
       </c>
     </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102">
+        <v>1.0207017291066283</v>
+      </c>
+      <c r="C102">
+        <v>0.97979797979797989</v>
+      </c>
       <c r="H102">
         <v>-5.50958E-2</v>
       </c>
@@ -7318,7 +7540,13 @@
         <v>-0.67304698132723595</v>
       </c>
     </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103">
+        <v>1.019765129682997</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
       <c r="H103">
         <v>-5.3588400000000001E-2</v>
       </c>
@@ -7326,7 +7554,7 @@
         <v>-0.66899667918776196</v>
       </c>
     </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H104">
         <v>-5.2078100000000002E-2</v>
       </c>
@@ -7334,7 +7562,7 @@
         <v>-0.66494637704828785</v>
       </c>
     </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H105">
         <v>-5.0598799999999999E-2</v>
       </c>
@@ -7342,7 +7570,7 @@
         <v>-0.66090151886330228</v>
       </c>
     </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H106">
         <v>-4.9169699999999997E-2</v>
       </c>
@@ -7350,7 +7578,7 @@
         <v>-0.65685121672382807</v>
       </c>
     </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H107">
         <v>-4.7715E-2</v>
       </c>
@@ -7358,7 +7586,7 @@
         <v>-0.65280091458435408</v>
       </c>
     </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H108">
         <v>-4.6219000000000003E-2</v>
       </c>
@@ -7366,7 +7594,7 @@
         <v>-0.64875061244487997</v>
       </c>
     </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H109">
         <v>-4.4704000000000001E-2</v>
       </c>
@@ -7374,7 +7602,7 @@
         <v>-0.6447057542598944</v>
       </c>
     </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H110">
         <v>-4.3091600000000001E-2</v>
       </c>
@@ -7382,7 +7610,7 @@
         <v>-0.6406554521204203</v>
       </c>
     </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H111">
         <v>-4.1565100000000001E-2</v>
       </c>
@@ -7390,7 +7618,7 @@
         <v>-0.63660514998094608</v>
       </c>
     </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H112">
         <v>-4.0083899999999999E-2</v>
       </c>
@@ -10544,51 +10772,51 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>5</v>
-      </c>
       <c r="L3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>-0.14197809798270894</v>
+        <v>-0.17197406340057636</v>
       </c>
       <c r="C4">
         <v>-0.9115258430592158</v>
@@ -10614,10 +10842,10 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>-0.1839265129682997</v>
+        <v>-0.171985590778098</v>
       </c>
       <c r="C5">
-        <v>-0.90350981099508754</v>
+        <v>-0.89132382285719569</v>
       </c>
       <c r="E5">
         <v>-0.2</v>
@@ -10640,10 +10868,10 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>-0.20689769452449566</v>
+        <v>-0.18953314121037465</v>
       </c>
       <c r="C6">
-        <v>-0.89148576289889514</v>
+        <v>-0.87112180265517536</v>
       </c>
       <c r="E6">
         <v>-0.2</v>
@@ -10666,10 +10894,10 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>-0.21482997118155622</v>
+        <v>-0.201164265129683</v>
       </c>
       <c r="C7">
-        <v>-0.87545369877063872</v>
+        <v>-0.85091978245315525</v>
       </c>
       <c r="E7">
         <v>-0.180952381</v>
@@ -10692,10 +10920,10 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>-0.21906340057636889</v>
+        <v>-0.20595677233429394</v>
       </c>
       <c r="C8">
-        <v>-0.86342965067444633</v>
+        <v>-0.83071776225113503</v>
       </c>
       <c r="E8">
         <v>-0.171428571</v>
@@ -10718,10 +10946,10 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>-0.22074207492795389</v>
+        <v>-0.20599999999999999</v>
       </c>
       <c r="C9">
-        <v>-0.85140560257825404</v>
+        <v>-0.81051574204911481</v>
       </c>
       <c r="E9">
         <v>-0.14920634899999999</v>
@@ -10744,10 +10972,10 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>-0.21827953890489912</v>
+        <v>-0.20576080691642651</v>
       </c>
       <c r="C10">
-        <v>-0.8353735384499974</v>
+        <v>-0.7903137218470947</v>
       </c>
       <c r="E10">
         <v>-0.126984127</v>
@@ -10770,10 +10998,10 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>-0.21684438040345821</v>
+        <v>-0.20412680115273774</v>
       </c>
       <c r="C11">
-        <v>-0.823349490353805</v>
+        <v>-0.77011170164507436</v>
       </c>
       <c r="E11">
         <v>-0.104761905</v>
@@ -10796,10 +11024,10 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>-0.21202017291066283</v>
+        <v>-0.20231844380403458</v>
       </c>
       <c r="C12">
-        <v>-0.81132544225761272</v>
+        <v>-0.74990968144305425</v>
       </c>
       <c r="E12">
         <v>-9.2063491999999997E-2</v>
@@ -10822,10 +11050,10 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>-0.21093371757925072</v>
+        <v>-0.19931700288184437</v>
       </c>
       <c r="C13">
-        <v>-0.79529337812935608</v>
+        <v>-0.72970766124103403</v>
       </c>
       <c r="E13">
         <v>-7.9365079000000005E-2</v>
@@ -10848,10 +11076,10 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>-0.20702305475504323</v>
+        <v>-0.19597982708933717</v>
       </c>
       <c r="C14">
-        <v>-0.78326933003316368</v>
+        <v>-0.70950564103901381</v>
       </c>
       <c r="E14">
         <v>-5.7142856999999998E-2</v>
@@ -10874,10 +11102,10 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>-0.20351008645533139</v>
+        <v>-0.19146974063400576</v>
       </c>
       <c r="C15">
-        <v>-0.77124528193697139</v>
+        <v>-0.6893036208369937</v>
       </c>
       <c r="E15">
         <v>-4.7619047999999997E-2</v>
@@ -10900,10 +11128,10 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>-0.19812247838616717</v>
+        <v>-0.18365417867435158</v>
       </c>
       <c r="C16">
-        <v>-0.75521321780871487</v>
+        <v>-0.66910160063497348</v>
       </c>
       <c r="E16">
         <v>-3.8095237999999997E-2</v>
@@ -10926,10 +11154,10 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>-0.19399423631123919</v>
+        <v>-0.17836023054755043</v>
       </c>
       <c r="C17">
-        <v>-0.74318916971252236</v>
+        <v>-0.64889958043295326</v>
       </c>
       <c r="E17">
         <v>-4.7619047999999997E-2</v>
@@ -10952,10 +11180,10 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>-0.18411239193083573</v>
+        <v>-0.17118011527377522</v>
       </c>
       <c r="C18">
-        <v>-0.73116512161633007</v>
+        <v>-0.62869756023093304</v>
       </c>
       <c r="E18">
         <v>-1.2698413E-2</v>
@@ -10978,10 +11206,10 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>-0.17318731988472622</v>
+        <v>-0.16378674351585015</v>
       </c>
       <c r="C19">
-        <v>-0.70310900939188115</v>
+        <v>-0.60849554002891282</v>
       </c>
       <c r="E19">
         <v>1.9047618999999998E-2</v>
@@ -11004,10 +11232,10 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>-0.16179682997118155</v>
+        <v>-0.15163688760806918</v>
       </c>
       <c r="C20">
-        <v>-0.67505289716743233</v>
+        <v>-0.5882935198268926</v>
       </c>
       <c r="E20">
         <v>3.4920634999999998E-2</v>
@@ -11030,10 +11258,10 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>-0.14875216138328529</v>
+        <v>-0.14299020172910665</v>
       </c>
       <c r="C21">
-        <v>-0.64699678494298329</v>
+        <v>-0.56809149962487238</v>
       </c>
       <c r="E21">
         <v>5.0793651000000002E-2</v>
@@ -11056,10 +11284,10 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>-0.1338021613832853</v>
+        <v>-0.13356642651296829</v>
       </c>
       <c r="C22">
-        <v>-0.62294868875059861</v>
+        <v>-0.54788947942285215</v>
       </c>
       <c r="E22">
         <v>7.3015872999999995E-2</v>
@@ -11082,10 +11310,10 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>-0.11763832853025938</v>
+        <v>-0.12340778097982709</v>
       </c>
       <c r="C23">
-        <v>-0.59489257652614969</v>
+        <v>-0.52768745922083193</v>
       </c>
       <c r="E23">
         <v>0.104761905</v>
@@ -11108,10 +11336,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>-9.9972622478386161E-2</v>
+        <v>-0.10560878962536023</v>
       </c>
       <c r="C24">
-        <v>-0.56683646430170076</v>
+        <v>-0.50748543901881171</v>
       </c>
       <c r="E24">
         <v>0.15555555600000001</v>
@@ -11134,10 +11362,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>-8.0070317002881849E-2</v>
+        <v>-9.1940345821325653E-2</v>
       </c>
       <c r="C25">
-        <v>-0.54278836810931608</v>
+        <v>-0.48728341881679149</v>
       </c>
       <c r="E25">
         <v>0.212698413</v>
@@ -11160,10 +11388,10 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>-5.7553602305475501E-2</v>
+        <v>-7.7961815561959649E-2</v>
       </c>
       <c r="C26">
-        <v>-0.51473225588486715</v>
+        <v>-0.46708139861477121</v>
       </c>
       <c r="E26">
         <v>0.257142857</v>
@@ -11186,10 +11414,10 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>-3.2787319884726225E-2</v>
+        <v>-5.4854322766570603E-2</v>
       </c>
       <c r="C27">
-        <v>-0.48667614366041823</v>
+        <v>-0.4468793784127511</v>
       </c>
       <c r="E27">
         <v>0.311111111</v>
@@ -11212,10 +11440,10 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>-6.2313400576368885E-3</v>
+        <v>-3.8118443804034584E-2</v>
       </c>
       <c r="C28">
-        <v>-0.46262804746803349</v>
+        <v>-0.42667735821073099</v>
       </c>
       <c r="E28">
         <v>0.36190476199999999</v>
@@ -11238,10 +11466,10 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>2.0546541786743516E-2</v>
+        <v>-2.0103025936599423E-2</v>
       </c>
       <c r="C29">
-        <v>-0.43457193524358462</v>
+        <v>-0.40647533800871077</v>
       </c>
       <c r="E29">
         <v>0.41587301599999998</v>
@@ -11264,10 +11492,10 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>5.0471469740634003E-2</v>
+        <v>-2.1360662824207489E-3</v>
       </c>
       <c r="C30">
-        <v>-0.40651582301913569</v>
+        <v>-0.38627331780669061</v>
       </c>
       <c r="E30">
         <v>0.482539683</v>
@@ -11290,10 +11518,10 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>8.2917291066282428E-2</v>
+        <v>2.7147694524495676E-2</v>
       </c>
       <c r="C31">
-        <v>-0.37845971079468682</v>
+        <v>-0.36607129760467028</v>
       </c>
       <c r="E31">
         <v>0.558730159</v>
@@ -11310,10 +11538,10 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>0.11798688760806918</v>
+        <v>4.8354034582132562E-2</v>
       </c>
       <c r="C32">
-        <v>-0.35441161460230203</v>
+        <v>-0.34586927740265011</v>
       </c>
       <c r="E32">
         <v>0.62539682500000005</v>
@@ -11330,10 +11558,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>0.15447262247838617</v>
+        <v>6.9692219020172905E-2</v>
       </c>
       <c r="C33">
-        <v>-0.32635550237785299</v>
+        <v>-0.32566725720063</v>
       </c>
       <c r="E33">
         <v>0.69206349199999995</v>
@@ -11350,10 +11578,10 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>0.19194524495677234</v>
+        <v>9.243775216138328E-2</v>
       </c>
       <c r="C34">
-        <v>-0.29829939015340418</v>
+        <v>-0.30546523699860978</v>
       </c>
       <c r="E34">
         <v>0.75873015899999996</v>
@@ -11370,10 +11598,10 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>0.23048126801152738</v>
+        <v>0.12929942363112393</v>
       </c>
       <c r="C35">
-        <v>-0.27425129396101938</v>
+        <v>-0.28526321679658961</v>
       </c>
       <c r="E35">
         <v>0.80634920600000004</v>
@@ -11390,10 +11618,10 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>0.27034438040345821</v>
+        <v>0.15445677233429395</v>
       </c>
       <c r="C36">
-        <v>-0.24619518173657051</v>
+        <v>-0.26506119659456928</v>
       </c>
       <c r="E36">
         <v>0.84761904799999999</v>
@@ -11410,10 +11638,10 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>0.30988040345821322</v>
+        <v>0.1802550432276657</v>
       </c>
       <c r="C37">
-        <v>-0.21813906951212159</v>
+        <v>-0.2448591763925492</v>
       </c>
       <c r="E37">
         <v>0.876190476</v>
@@ -11430,10 +11658,10 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>0.35246541786743513</v>
+        <v>0.22047406340057635</v>
       </c>
       <c r="C38">
-        <v>-0.19008295728767269</v>
+        <v>-0.22465715619052901</v>
       </c>
       <c r="E38">
         <v>0.91428571400000003</v>
@@ -11450,10 +11678,10 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>0.39430979827089341</v>
+        <v>0.24727377521613833</v>
       </c>
       <c r="C39">
-        <v>-0.16603486109528789</v>
+        <v>-0.20445513598850881</v>
       </c>
       <c r="E39">
         <v>0.95873015900000003</v>
@@ -11470,10 +11698,10 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>0.43719884726224784</v>
+        <v>0.27564985590778096</v>
       </c>
       <c r="C40">
-        <v>-0.13797874887083911</v>
+        <v>-0.18425311578648851</v>
       </c>
       <c r="E40">
         <v>0.97777777799999999</v>
@@ -11490,10 +11718,10 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>0.48062536023054753</v>
+        <v>0.30465850144092216</v>
       </c>
       <c r="C41">
-        <v>-0.10992263664639031</v>
+        <v>-0.16405109558446829</v>
       </c>
       <c r="E41">
         <v>0.99682539699999995</v>
@@ -11510,10 +11738,10 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>0.52351585014409219</v>
+        <v>0.34847550432276658</v>
       </c>
       <c r="C42">
-        <v>-8.5874540454005374E-2</v>
+        <v>-0.1438490753824482</v>
       </c>
       <c r="E42">
         <v>1.0063492060000001</v>
@@ -11530,10 +11758,10 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>0.56817867435158498</v>
+        <v>0.37921613832853024</v>
       </c>
       <c r="C43">
-        <v>-5.7818428229556407E-2</v>
+        <v>-0.1236470551804279</v>
       </c>
       <c r="E43">
         <v>1.015873016</v>
@@ -11550,10 +11778,10 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>0.61239193083573484</v>
+        <v>0.41056051873198846</v>
       </c>
       <c r="C44">
-        <v>-2.976231600510764E-2</v>
+        <v>-0.10344503497840769</v>
       </c>
       <c r="E44">
         <v>1.015873016</v>
@@ -11570,10 +11798,10 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>0.65171469740634014</v>
+        <v>0.44144956772334293</v>
       </c>
       <c r="C45">
-        <v>-1.706203780658861E-3</v>
+        <v>-8.3243014776387611E-2</v>
       </c>
       <c r="E45">
         <v>1.019047619</v>
@@ -11590,10 +11818,10 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>0.68920893371757919</v>
+        <v>0.48888328530259367</v>
       </c>
       <c r="C46">
-        <v>2.2341892411726041E-2</v>
+        <v>-6.3040994574367307E-2</v>
       </c>
       <c r="E46">
         <v>1.019047619</v>
@@ -11610,10 +11838,10 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>0.7266412103746398</v>
+        <v>0.52078097982708937</v>
       </c>
       <c r="C47">
-        <v>5.0398004636174998E-2</v>
+        <v>-4.2838974372346988E-2</v>
       </c>
       <c r="E47">
         <v>1.015873016</v>
@@ -11630,10 +11858,10 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>0.75631268011527375</v>
+        <v>0.55309077809798279</v>
       </c>
       <c r="C48">
-        <v>7.8454116860623965E-2</v>
+        <v>-2.2636954170326861E-2</v>
       </c>
       <c r="E48">
         <v>1.0063492060000001</v>
@@ -11650,10 +11878,10 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.78310662824207489</v>
+        <v>0.586592219020173</v>
       </c>
       <c r="C49">
-        <v>0.1025022130530087</v>
+        <v>-2.4349339683067358E-3</v>
       </c>
       <c r="E49">
         <v>1.015873016</v>
@@ -11670,10 +11898,10 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.80464121037463987</v>
+        <v>0.63466138328530253</v>
       </c>
       <c r="C50">
-        <v>0.13055832527745759</v>
+        <v>1.7767086233713581E-2</v>
       </c>
       <c r="E50">
         <v>1.015873016</v>
@@ -11690,10 +11918,10 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.8219380403458213</v>
+        <v>0.66666858789625361</v>
       </c>
       <c r="C51">
-        <v>0.1586144375019064</v>
+        <v>3.7969106435733702E-2</v>
       </c>
       <c r="E51">
         <v>1.019047619</v>
@@ -11710,10 +11938,10 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.83792507204610944</v>
+        <v>0.6967262247838617</v>
       </c>
       <c r="C52">
-        <v>0.18667054972635519</v>
+        <v>5.8171126637753832E-2</v>
       </c>
       <c r="E52">
         <v>1.015873016</v>
@@ -11730,10 +11958,10 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.84946541786743512</v>
+        <v>0.7408472622478387</v>
       </c>
       <c r="C53">
-        <v>0.21071864591874009</v>
+        <v>7.8373146839774144E-2</v>
       </c>
       <c r="H53">
         <v>-0.158498</v>
@@ -11744,10 +11972,10 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.85838040345821331</v>
+        <v>0.76650000000000007</v>
       </c>
       <c r="C54">
-        <v>0.2387747581431891</v>
+        <v>9.8575167041794268E-2</v>
       </c>
       <c r="H54">
         <v>-0.15667</v>
@@ -11758,10 +11986,10 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.86644236311239198</v>
+        <v>0.7907968299711815</v>
       </c>
       <c r="C55">
-        <v>0.26683087036763792</v>
+        <v>0.1187771872438146</v>
       </c>
       <c r="H55">
         <v>-0.15479499999999999</v>
@@ -11772,10 +12000,10 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.87335446685878959</v>
+        <v>0.81221902017291059</v>
       </c>
       <c r="C56">
-        <v>0.29087896656002282</v>
+        <v>0.1389792074458347</v>
       </c>
       <c r="H56">
         <v>-0.152861</v>
@@ -11786,10 +12014,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.87950432276657053</v>
+        <v>0.83878242074927956</v>
       </c>
       <c r="C57">
-        <v>0.31893507878447169</v>
+        <v>0.15918122764785481</v>
       </c>
       <c r="H57">
         <v>-0.15095</v>
@@ -11800,10 +12028,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.88583285302593662</v>
+        <v>0.85350864553314121</v>
       </c>
       <c r="C58">
-        <v>0.34699119100892051</v>
+        <v>0.17938324784987511</v>
       </c>
       <c r="H58">
         <v>-0.149115</v>
@@ -11814,10 +12042,10 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.89199135446685884</v>
+        <v>0.86630403458213256</v>
       </c>
       <c r="C59">
-        <v>0.37103928720130519</v>
+        <v>0.1995852680518953</v>
       </c>
       <c r="H59">
         <v>-0.14719499999999999</v>
@@ -11828,10 +12056,10 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.89800000000000002</v>
+        <v>0.87782420749279544</v>
       </c>
       <c r="C60">
-        <v>0.39909539942575423</v>
+        <v>0.21978728825391541</v>
       </c>
       <c r="H60">
         <v>-0.14524100000000001</v>
@@ -11842,10 +12070,10 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.90370749279538909</v>
+        <v>0.89292074927953891</v>
       </c>
       <c r="C61">
-        <v>0.42715151165020321</v>
+        <v>0.23998930845593569</v>
       </c>
       <c r="H61">
         <v>-0.14326700000000001</v>
@@ -11856,10 +12084,10 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.90916426512968307</v>
+        <v>0.90170461095100862</v>
       </c>
       <c r="C62">
-        <v>0.45520762387465191</v>
+        <v>0.26019132865795558</v>
       </c>
       <c r="H62">
         <v>-0.14127100000000001</v>
@@ -11870,10 +12098,10 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>0.91443227665706051</v>
+        <v>0.90963688760806916</v>
       </c>
       <c r="C63">
-        <v>0.47925572006703637</v>
+        <v>0.28039334885997602</v>
       </c>
       <c r="H63">
         <v>-0.13910900000000001</v>
@@ -11884,10 +12112,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>0.92013400576368876</v>
+        <v>0.91671469740634015</v>
       </c>
       <c r="C64">
-        <v>0.50731183229148558</v>
+        <v>0.3005953690619963</v>
       </c>
       <c r="H64">
         <v>-0.13697200000000001</v>
@@ -11898,10 +12126,10 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>0.92538472622478385</v>
+        <v>0.92735014409221905</v>
       </c>
       <c r="C65">
-        <v>0.53536794451593461</v>
+        <v>0.32079738926401619</v>
       </c>
       <c r="H65">
         <v>-0.134903</v>
@@ -11912,10 +12140,10 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>0.93088184438040356</v>
+        <v>0.93405475504322777</v>
       </c>
       <c r="C66">
-        <v>0.55941604070831907</v>
+        <v>0.34099940946603652</v>
       </c>
       <c r="H66">
         <v>-0.132856</v>
@@ -11926,10 +12154,10 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>0.93622478386167152</v>
+        <v>0.94073198847262252</v>
       </c>
       <c r="C67">
-        <v>0.58747215293276844</v>
+        <v>0.36120142966805668</v>
       </c>
       <c r="H67">
         <v>-0.130801</v>
@@ -11940,10 +12168,10 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>0.94143371757925076</v>
+        <v>0.94978386167146966</v>
       </c>
       <c r="C68">
-        <v>0.61552826515721704</v>
+        <v>0.38140344987007718</v>
       </c>
       <c r="H68">
         <v>-0.12876199999999999</v>
@@ -11954,10 +12182,10 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>0.94682132564841504</v>
+        <v>0.95578818443804037</v>
       </c>
       <c r="C69">
-        <v>0.64358437738166618</v>
+        <v>0.40160547007209729</v>
       </c>
       <c r="H69">
         <v>-0.126723</v>
@@ -11968,10 +12196,10 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>0.95233861671469744</v>
+        <v>0.96104899135446675</v>
       </c>
       <c r="C70">
-        <v>0.66763247357405053</v>
+        <v>0.4218074902741174</v>
       </c>
       <c r="H70">
         <v>-0.12461999999999999</v>
@@ -11982,10 +12210,10 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>0.95755907780979832</v>
+        <v>0.9662276657060519</v>
       </c>
       <c r="C71">
-        <v>0.69568858579849946</v>
+        <v>0.44200951047613768</v>
       </c>
       <c r="H71">
         <v>-0.12242699999999999</v>
@@ -11996,10 +12224,10 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>0.96253890489913541</v>
+        <v>0.97380691642651296</v>
       </c>
       <c r="C72">
-        <v>0.72374469802294839</v>
+        <v>0.46221153067815779</v>
       </c>
       <c r="H72">
         <v>-0.12023499999999999</v>
@@ -12010,10 +12238,10 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>0.96717579250720465</v>
+        <v>0.97861959654178676</v>
       </c>
       <c r="C73">
-        <v>0.74779279421533318</v>
+        <v>0.48241355088017818</v>
       </c>
       <c r="H73">
         <v>-0.118058</v>
@@ -12024,10 +12252,10 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>0.97157636887608068</v>
+        <v>0.98336599423631121</v>
       </c>
       <c r="C74">
-        <v>0.7758489064397821</v>
+        <v>0.50261557108219868</v>
       </c>
       <c r="H74">
         <v>-0.11590499999999999</v>
@@ -12038,10 +12266,10 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>0.97569308357348694</v>
+        <v>0.98786455331412104</v>
       </c>
       <c r="C75">
-        <v>0.80390501866423103</v>
+        <v>0.52281759128421845</v>
       </c>
       <c r="H75">
         <v>-0.113742</v>
@@ -12052,10 +12280,10 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>0.97945100864553314</v>
+        <v>0.99448991354466865</v>
       </c>
       <c r="C76">
-        <v>0.83196113088868007</v>
+        <v>0.54301961148623878</v>
       </c>
       <c r="H76">
         <v>-0.11150500000000001</v>
@@ -12066,10 +12294,10 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>0.98280115273775215</v>
+        <v>0.99859510086455328</v>
       </c>
       <c r="C77">
-        <v>0.85600922708106475</v>
+        <v>0.56322163168825923</v>
       </c>
       <c r="H77">
         <v>-0.109305</v>
@@ -12080,10 +12308,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>0.98585878962536033</v>
+        <v>1.0022939481268012</v>
       </c>
       <c r="C78">
-        <v>0.88406533930551368</v>
+        <v>0.58342365189027934</v>
       </c>
       <c r="H78">
         <v>-0.107117</v>
@@ -12094,10 +12322,10 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>0.98853602305475496</v>
+        <v>1.0059740634005763</v>
       </c>
       <c r="C79">
-        <v>0.91212145152996227</v>
+        <v>0.60362567209229934</v>
       </c>
       <c r="H79">
         <v>-0.104874</v>
@@ -12108,10 +12336,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>0.99086887608069163</v>
+        <v>1.0108386167146974</v>
       </c>
       <c r="C80">
-        <v>0.93616954772234739</v>
+        <v>0.62382769229431945</v>
       </c>
       <c r="H80">
         <v>-0.102622</v>
@@ -12122,10 +12350,10 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>0.99279394812680122</v>
+        <v>1.0139567723342939</v>
       </c>
       <c r="C81">
-        <v>0.96422565994679632</v>
+        <v>0.64402971249633956</v>
       </c>
       <c r="H81">
         <v>-0.10037500000000001</v>
@@ -12136,10 +12364,10 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>0.99434149855907783</v>
+        <v>1.0167752161383286</v>
       </c>
       <c r="C82">
-        <v>0.99228177217124491</v>
+        <v>0.66423173269836022</v>
       </c>
       <c r="H82">
         <v>-9.8067199999999993E-2</v>
@@ -12150,10 +12378,10 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>0.9955518731988473</v>
+        <v>1.0203674351585015</v>
       </c>
       <c r="C83">
-        <v>1.0203378843956941</v>
+        <v>0.68443375290037978</v>
       </c>
       <c r="H83">
         <v>-9.5654400000000001E-2</v>
@@ -12164,10 +12392,10 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>0.99645533141210374</v>
+        <v>1.0224481268011527</v>
       </c>
       <c r="C84">
-        <v>1.0443859805880791</v>
+        <v>0.70463577310240033</v>
       </c>
       <c r="H84">
         <v>-9.3303499999999998E-2</v>
@@ -12178,10 +12406,10 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>0.99714409221902023</v>
+        <v>1.0242420749279537</v>
       </c>
       <c r="C85">
-        <v>1.072442092812528</v>
+        <v>0.72483779330442044</v>
       </c>
       <c r="H85">
         <v>-9.0978000000000003E-2</v>
@@ -12191,6 +12419,12 @@
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>1.0257291066282421</v>
+      </c>
+      <c r="C86">
+        <v>0.74503981350644055</v>
+      </c>
       <c r="H86">
         <v>-8.8662099999999994E-2</v>
       </c>
@@ -12199,6 +12433,12 @@
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>1.0275129682997119</v>
+      </c>
+      <c r="C87">
+        <v>0.76524183370846111</v>
+      </c>
       <c r="H87">
         <v>-8.6339899999999997E-2</v>
       </c>
@@ -12207,6 +12447,12 @@
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>1.028335734870317</v>
+      </c>
+      <c r="C88">
+        <v>0.78544385391048122</v>
+      </c>
       <c r="H88">
         <v>-8.4012600000000007E-2</v>
       </c>
@@ -12215,6 +12461,12 @@
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>1.0288933717579252</v>
+      </c>
+      <c r="C89">
+        <v>0.80564587411250133</v>
+      </c>
       <c r="H89">
         <v>-8.1685300000000002E-2</v>
       </c>
@@ -12223,6 +12475,12 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>1.0292017291066282</v>
+      </c>
+      <c r="C90">
+        <v>0.82584789431452177</v>
+      </c>
       <c r="H90">
         <v>-7.9290200000000005E-2</v>
       </c>
@@ -12231,6 +12489,12 @@
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>1.0292752161383285</v>
+      </c>
+      <c r="C91">
+        <v>0.84604991451654155</v>
+      </c>
       <c r="H91">
         <v>-7.6851199999999995E-2</v>
       </c>
@@ -12239,6 +12503,12 @@
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>1.0291268011527379</v>
+      </c>
+      <c r="C92">
+        <v>0.8662519347185621</v>
+      </c>
       <c r="H92">
         <v>-7.4412300000000001E-2</v>
       </c>
@@ -12247,6 +12517,12 @@
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>1.0287780979827088</v>
+      </c>
+      <c r="C93">
+        <v>0.88645395492058221</v>
+      </c>
       <c r="H93">
         <v>-7.1934600000000001E-2</v>
       </c>
@@ -12255,6 +12531,12 @@
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>1.0280302593659942</v>
+      </c>
+      <c r="C94">
+        <v>0.90665597512260232</v>
+      </c>
       <c r="H94">
         <v>-6.9404999999999994E-2</v>
       </c>
@@ -12263,6 +12545,12 @@
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>1.0273674351585016</v>
+      </c>
+      <c r="C95">
+        <v>0.92685799532462243</v>
+      </c>
       <c r="H95">
         <v>-6.6944299999999998E-2</v>
       </c>
@@ -12271,6 +12559,12 @@
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>1.0265821325648414</v>
+      </c>
+      <c r="C96">
+        <v>0.94706001552664298</v>
+      </c>
       <c r="H96">
         <v>-6.4528500000000003E-2</v>
       </c>
@@ -12278,7 +12572,13 @@
         <v>-0.64426479394632263</v>
       </c>
     </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>1.0256729106628242</v>
+      </c>
+      <c r="C97">
+        <v>0.96726203572866309</v>
+      </c>
       <c r="H97">
         <v>-6.21127E-2</v>
       </c>
@@ -12286,7 +12586,13 @@
         <v>-0.64021449180684842</v>
       </c>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>1.0240129682997117</v>
+      </c>
+      <c r="C98">
+        <v>0.9874640559306832</v>
+      </c>
       <c r="H98">
         <v>-5.9696800000000001E-2</v>
       </c>
@@ -12294,7 +12600,13 @@
         <v>-0.63616963362186285</v>
       </c>
     </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99">
+        <v>1.0227391930835734</v>
+      </c>
+      <c r="C99">
+        <v>1.007666076132703</v>
+      </c>
       <c r="H99">
         <v>-5.7248199999999999E-2</v>
       </c>
@@ -12302,7 +12614,13 @@
         <v>-0.63211933148238875</v>
       </c>
     </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100">
+        <v>1.0213443804034581</v>
+      </c>
+      <c r="C100">
+        <v>1.027868096334724</v>
+      </c>
       <c r="H100">
         <v>-5.4747299999999999E-2</v>
       </c>
@@ -12310,7 +12628,13 @@
         <v>-0.62807447329740318</v>
       </c>
     </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B101">
+        <v>1.0197968299711817</v>
+      </c>
+      <c r="C101">
+        <v>1.0480701165367441</v>
+      </c>
       <c r="H101">
         <v>-5.2152799999999999E-2</v>
       </c>
@@ -12318,7 +12642,13 @@
         <v>-0.62402417115792908</v>
       </c>
     </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102">
+        <v>1.017301152737752</v>
+      </c>
+      <c r="C102">
+        <v>1.068272136738764</v>
+      </c>
       <c r="H102">
         <v>-4.9501299999999998E-2</v>
       </c>
@@ -12326,7 +12656,13 @@
         <v>-0.61997386901845497</v>
       </c>
     </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103">
+        <v>1.0155259365994236</v>
+      </c>
+      <c r="C103">
+        <v>1.0884741569407841</v>
+      </c>
       <c r="H103">
         <v>-4.68774E-2</v>
       </c>
@@ -12334,7 +12670,7 @@
         <v>-0.6159290108334694</v>
       </c>
     </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H104">
         <v>-4.4254700000000001E-2</v>
       </c>
@@ -12342,7 +12678,7 @@
         <v>-0.6118787086939953</v>
       </c>
     </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H105">
         <v>-4.1636300000000001E-2</v>
       </c>
@@ -12350,7 +12686,7 @@
         <v>-0.60782840655452119</v>
       </c>
     </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H106">
         <v>-3.9028800000000002E-2</v>
       </c>
@@ -12358,7 +12694,7 @@
         <v>-0.60378354836953563</v>
       </c>
     </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H107">
         <v>-3.6408000000000003E-2</v>
       </c>
@@ -12366,7 +12702,7 @@
         <v>-0.59973324623006152</v>
       </c>
     </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H108">
         <v>-3.3748199999999999E-2</v>
       </c>
@@ -12374,7 +12710,7 @@
         <v>-0.59568294409058742</v>
       </c>
     </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H109">
         <v>-3.10776E-2</v>
       </c>
@@ -12382,7 +12718,7 @@
         <v>-0.59163808590560174</v>
       </c>
     </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H110">
         <v>-2.8437799999999999E-2</v>
       </c>
@@ -12390,7 +12726,7 @@
         <v>-0.58758778376612775</v>
       </c>
     </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H111">
         <v>-2.5685199999999998E-2</v>
       </c>
@@ -12398,7 +12734,7 @@
         <v>-0.58354292558114207</v>
       </c>
     </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H112">
         <v>-2.2987E-2</v>
       </c>
@@ -15560,51 +15896,51 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>5</v>
-      </c>
       <c r="L3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>-9.2262103746397692E-2</v>
+        <v>-0.10252593659942363</v>
       </c>
       <c r="C4">
         <v>-0.50002689184101534</v>
@@ -15630,10 +15966,10 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>-0.11642420749279539</v>
+        <v>-0.13244048991354468</v>
       </c>
       <c r="C5">
-        <v>-0.48798829304928348</v>
+        <v>-0.47980042451079941</v>
       </c>
       <c r="E5">
         <v>-9.4936708999999994E-2</v>
@@ -15656,10 +15992,10 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>-0.10446541786743516</v>
+        <v>-0.12547391930835736</v>
       </c>
       <c r="C6">
-        <v>-0.47594969425755179</v>
+        <v>-0.4595739571805833</v>
       </c>
       <c r="E6">
         <v>-7.9113924000000002E-2</v>
@@ -15682,10 +16018,10 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>-0.10180533141210375</v>
+        <v>-0.11418458213256484</v>
       </c>
       <c r="C7">
-        <v>-0.45989822920190943</v>
+        <v>-0.43934748985036709</v>
       </c>
       <c r="E7">
         <v>-4.7468353999999997E-2</v>
@@ -15708,10 +16044,10 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>-9.0957636887608065E-2</v>
+        <v>-9.6576657060518725E-2</v>
       </c>
       <c r="C8">
-        <v>-0.44785963041017762</v>
+        <v>-0.41912102252015121</v>
       </c>
       <c r="E8">
         <v>3.1645570000000001E-3</v>
@@ -15734,10 +16070,10 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>-8.4878530259365995E-2</v>
+        <v>-8.2492795389048995E-2</v>
       </c>
       <c r="C9">
-        <v>-0.43180816535453509</v>
+        <v>-0.39889455518993511</v>
       </c>
       <c r="E9">
         <v>3.7974684000000002E-2</v>
@@ -15760,10 +16096,10 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>-7.3574495677233426E-2</v>
+        <v>-6.8038040345821324E-2</v>
       </c>
       <c r="C10">
-        <v>-0.41976956656280329</v>
+        <v>-0.37866808785971889</v>
       </c>
       <c r="E10">
         <v>8.2278481000000001E-2</v>
@@ -15786,10 +16122,10 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>-6.4622622478386169E-2</v>
+        <v>-5.3626368876080695E-2</v>
       </c>
       <c r="C11">
-        <v>-0.40773096777107148</v>
+        <v>-0.35844162052950312</v>
       </c>
       <c r="E11">
         <v>0.12341772199999999</v>
@@ -15812,10 +16148,10 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>-5.1913256484149857E-2</v>
+        <v>-2.9128386167146973E-2</v>
       </c>
       <c r="C12">
-        <v>-0.39167950271542917</v>
+        <v>-0.33821515319928702</v>
       </c>
       <c r="E12">
         <v>0.17721518999999999</v>
@@ -15838,10 +16174,10 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>-4.1151008645533144E-2</v>
+        <v>-1.1486527377521615E-2</v>
       </c>
       <c r="C13">
-        <v>-0.37964090392369743</v>
+        <v>-0.31798868586907092</v>
       </c>
       <c r="E13">
         <v>0.221518987</v>
@@ -15864,10 +16200,10 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>-2.8131844380403455E-2</v>
+        <v>7.6022766570605187E-3</v>
       </c>
       <c r="C14">
-        <v>-0.36760230513196562</v>
+        <v>-0.29776221853885482</v>
       </c>
       <c r="E14">
         <v>0.25632911400000002</v>
@@ -15890,10 +16226,10 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>-1.6272046109510087E-2</v>
+        <v>3.7661671469740636E-2</v>
       </c>
       <c r="C15">
-        <v>-0.35155084007632298</v>
+        <v>-0.27753575120863883</v>
       </c>
       <c r="E15">
         <v>0.300632911</v>
@@ -15916,10 +16252,10 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>-1.2213789625360231E-3</v>
+        <v>6.0816282420749275E-2</v>
       </c>
       <c r="C16">
-        <v>-0.33951224128459129</v>
+        <v>-0.25730928387842272</v>
       </c>
       <c r="E16">
         <v>0.32594936699999999</v>
@@ -15942,10 +16278,10 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>2.3875072046109509E-2</v>
+        <v>8.4062391930835742E-2</v>
       </c>
       <c r="C17">
-        <v>-0.3274736424928596</v>
+        <v>-0.2370828165482067</v>
       </c>
       <c r="E17">
         <v>0.36708860799999998</v>
@@ -15962,10 +16298,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>5.5173775216138324E-2</v>
+        <v>0.10880835734870317</v>
       </c>
       <c r="C18">
-        <v>-0.29938357864548543</v>
+        <v>-0.2168563492179906</v>
       </c>
       <c r="E18">
         <v>0.40189873399999998</v>
@@ -15982,10 +16318,10 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>8.8105331412103749E-2</v>
+        <v>0.14764409221902017</v>
       </c>
       <c r="C19">
-        <v>-0.27129351479811098</v>
+        <v>-0.19662988188777461</v>
       </c>
       <c r="E19">
         <v>0.42405063300000001</v>
@@ -16002,10 +16338,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>0.12439798270893372</v>
+        <v>0.1757492795389049</v>
       </c>
       <c r="C20">
-        <v>-0.24721631721464751</v>
+        <v>-0.17640341455755859</v>
       </c>
       <c r="E20">
         <v>0.436708861</v>
@@ -16022,10 +16358,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>0.16357780979827088</v>
+        <v>0.20415994236311241</v>
       </c>
       <c r="C21">
-        <v>-0.21912625336727329</v>
+        <v>-0.15617694722734249</v>
       </c>
       <c r="E21">
         <v>0.45569620300000002</v>
@@ -16042,10 +16378,10 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>0.20430691642651294</v>
+        <v>0.23429250720461092</v>
       </c>
       <c r="C22">
-        <v>-0.19103618951989931</v>
+        <v>-0.13595047989712639</v>
       </c>
       <c r="E22">
         <v>0.49050632900000002</v>
@@ -16062,10 +16398,10 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>0.24590922190201731</v>
+        <v>0.28064841498559079</v>
       </c>
       <c r="C23">
-        <v>-0.16294612567252501</v>
+        <v>-0.11572401256691039</v>
       </c>
       <c r="E23">
         <v>0.54113924099999999</v>
@@ -16082,10 +16418,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>0.29022478386167144</v>
+        <v>0.31323775216138328</v>
       </c>
       <c r="C24">
-        <v>-0.1388689280890614</v>
+        <v>-9.5497545236694181E-2</v>
       </c>
       <c r="E24">
         <v>0.58544303799999997</v>
@@ -16102,10 +16438,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>0.33443804034582131</v>
+        <v>0.34661383285302594</v>
       </c>
       <c r="C25">
-        <v>-0.11077886424168711</v>
+        <v>-7.5271077906478343E-2</v>
       </c>
       <c r="E25">
         <v>0.65189873399999998</v>
@@ -16122,10 +16458,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>0.38043371757925076</v>
+        <v>0.39729682997118154</v>
       </c>
       <c r="C26">
-        <v>-8.268880039431295E-2</v>
+        <v>-5.5044610576262303E-2</v>
       </c>
       <c r="E26">
         <v>0.70886075900000001</v>
@@ -16142,10 +16478,10 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>0.42511959654178677</v>
+        <v>0.43067146974063403</v>
       </c>
       <c r="C27">
-        <v>-5.8611602810849477E-2</v>
+        <v>-3.4818143246046082E-2</v>
       </c>
       <c r="E27">
         <v>0.76265822800000005</v>
@@ -16162,10 +16498,10 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>0.47218731988472618</v>
+        <v>0.4641051873198847</v>
       </c>
       <c r="C28">
-        <v>-3.0521538963475162E-2</v>
+        <v>-1.4591675915830229E-2</v>
       </c>
       <c r="E28">
         <v>0.81962025299999997</v>
@@ -16182,10 +16518,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>0.52070028818443803</v>
+        <v>0.49832564841498561</v>
       </c>
       <c r="C29">
-        <v>-2.4314751161008332E-3</v>
+        <v>5.6347914143861791E-3</v>
       </c>
       <c r="E29">
         <v>0.87025316500000005</v>
@@ -16202,10 +16538,10 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>0.56591786743515848</v>
+        <v>0.54940634005763689</v>
       </c>
       <c r="C30">
-        <v>2.164572246736263E-2</v>
+        <v>2.5861258744602031E-2</v>
       </c>
       <c r="E30">
         <v>0.90506329100000005</v>
@@ -16222,10 +16558,10 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>0.60827089337175788</v>
+        <v>0.58307636887608061</v>
       </c>
       <c r="C31">
-        <v>4.9735786314736588E-2</v>
+        <v>4.6087726074817877E-2</v>
       </c>
       <c r="E31">
         <v>0.94620253200000004</v>
@@ -16242,10 +16578,10 @@
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>0.64812968299711815</v>
+        <v>0.61828242074927953</v>
       </c>
       <c r="C32">
-        <v>7.782585016211091E-2</v>
+        <v>6.6314193405034291E-2</v>
       </c>
       <c r="E32">
         <v>0.97151898699999995</v>
@@ -16262,10 +16598,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>0.6842190201729107</v>
+        <v>0.65062391930835739</v>
       </c>
       <c r="C33">
-        <v>0.1059159140094854</v>
+        <v>8.6540660735250324E-2</v>
       </c>
       <c r="E33">
         <v>0.98734177199999995</v>
@@ -16282,10 +16618,10 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>0.71580547550432272</v>
+        <v>0.6971945244956772</v>
       </c>
       <c r="C34">
-        <v>0.12999311159294871</v>
+        <v>0.1067671280654662</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -16302,10 +16638,10 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>0.74441066282420743</v>
+        <v>0.72557780979827091</v>
       </c>
       <c r="C35">
-        <v>0.15808317544032299</v>
+        <v>0.12699359539568239</v>
       </c>
       <c r="E35">
         <v>1.0158227849999999</v>
@@ -16322,10 +16658,10 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>0.76982853025936593</v>
+        <v>0.75160374639769456</v>
       </c>
       <c r="C36">
-        <v>0.18617323928769741</v>
+        <v>0.14722006272589841</v>
       </c>
       <c r="E36">
         <v>1.022151899</v>
@@ -16342,10 +16678,10 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>0.79063256484149846</v>
+        <v>0.78930547550432284</v>
       </c>
       <c r="C37">
-        <v>0.2102504368711606</v>
+        <v>0.16744653005611429</v>
       </c>
       <c r="E37">
         <v>1.0253164560000001</v>
@@ -16362,10 +16698,10 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>0.80937463976945245</v>
+        <v>0.81180979827089328</v>
       </c>
       <c r="C38">
-        <v>0.23834050071853499</v>
+        <v>0.1876729973863305</v>
       </c>
       <c r="E38">
         <v>1.018987342</v>
@@ -16382,10 +16718,10 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>0.82530115273775217</v>
+        <v>0.83167291066282423</v>
       </c>
       <c r="C39">
-        <v>0.2664305645659093</v>
+        <v>0.20789946471654661</v>
       </c>
       <c r="E39">
         <v>1.022151899</v>
@@ -16402,10 +16738,10 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>0.84053746397694518</v>
+        <v>0.84911815561959658</v>
       </c>
       <c r="C40">
-        <v>0.29050776214937291</v>
+        <v>0.2281259320467624</v>
       </c>
       <c r="E40">
         <v>1.0348101270000001</v>
@@ -16422,10 +16758,10 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>0.85334149855907793</v>
+        <v>0.87138184438040356</v>
       </c>
       <c r="C41">
-        <v>0.31859782599674719</v>
+        <v>0.24835239937697859</v>
       </c>
       <c r="E41">
         <v>1.041139241</v>
@@ -16442,10 +16778,10 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>0.86550144092219028</v>
+        <v>0.88461383285302597</v>
       </c>
       <c r="C42">
-        <v>0.34668788984412119</v>
+        <v>0.26857886670719472</v>
       </c>
       <c r="E42">
         <v>1.0379746839999999</v>
@@ -16462,10 +16798,10 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>0.87711959654178673</v>
+        <v>0.89650864553314125</v>
       </c>
       <c r="C43">
-        <v>0.37477795369149541</v>
+        <v>0.28880533403741049</v>
       </c>
       <c r="E43">
         <v>1.0506329109999999</v>
@@ -16482,10 +16818,10 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>0.88804755043227657</v>
+        <v>0.90779971181556196</v>
       </c>
       <c r="C44">
-        <v>0.3988551512749588</v>
+        <v>0.30903180136762692</v>
       </c>
       <c r="E44">
         <v>1.044303797</v>
@@ -16502,10 +16838,10 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>0.89884582132564839</v>
+        <v>0.92312391930835735</v>
       </c>
       <c r="C45">
-        <v>0.42694521512233308</v>
+        <v>0.32925826869784269</v>
       </c>
       <c r="H45">
         <v>-4.7304899999999997E-2</v>
@@ -16516,10 +16852,10 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>0.90907780979827091</v>
+        <v>0.93224783861671467</v>
       </c>
       <c r="C46">
-        <v>0.45503527896970752</v>
+        <v>0.34948473602805857</v>
       </c>
       <c r="H46">
         <v>-4.2914000000000001E-2</v>
@@ -16530,10 +16866,10 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>0.91819164265129682</v>
+        <v>0.9407708933717579</v>
       </c>
       <c r="C47">
-        <v>0.47911247655317107</v>
+        <v>0.36971120335827479</v>
       </c>
       <c r="H47">
         <v>-3.8528300000000001E-2</v>
@@ -16544,10 +16880,10 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>0.92675936599423636</v>
+        <v>0.95225648414985586</v>
       </c>
       <c r="C48">
-        <v>0.50720254040054524</v>
+        <v>0.38993767068849078</v>
       </c>
       <c r="H48">
         <v>-3.4065400000000003E-2</v>
@@ -16558,10 +16894,10 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.93484870317002877</v>
+        <v>0.95967435158501446</v>
       </c>
       <c r="C49">
-        <v>0.53529260424791936</v>
+        <v>0.41016413801870671</v>
       </c>
       <c r="H49">
         <v>-2.9571699999999999E-2</v>
@@ -16572,10 +16908,10 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.94241498559077796</v>
+        <v>0.96643371757925078</v>
       </c>
       <c r="C50">
-        <v>0.55936980183138307</v>
+        <v>0.43039060534892332</v>
       </c>
       <c r="H50">
         <v>-2.5053599999999999E-2</v>
@@ -16586,10 +16922,10 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.94960518731988464</v>
+        <v>0.97256916426512963</v>
       </c>
       <c r="C51">
-        <v>0.58745986567875741</v>
+        <v>0.45061707267913942</v>
       </c>
       <c r="H51">
         <v>-2.04213E-2</v>
@@ -16600,10 +16936,10 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.95627089337175797</v>
+        <v>0.98093515850144097</v>
       </c>
       <c r="C52">
-        <v>0.61554992952613152</v>
+        <v>0.47084354000935558</v>
       </c>
       <c r="H52">
         <v>-1.5744299999999999E-2</v>
@@ -16614,10 +16950,10 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.96254610951008635</v>
+        <v>0.9857593659942363</v>
       </c>
       <c r="C53">
-        <v>0.64363999337350564</v>
+        <v>0.4910700073395714</v>
       </c>
       <c r="H53">
         <v>-1.10064E-2</v>
@@ -16628,10 +16964,10 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.96834438040345816</v>
+        <v>0.99038904899135449</v>
       </c>
       <c r="C54">
-        <v>0.66771719095696924</v>
+        <v>0.51129647466978767</v>
       </c>
       <c r="H54">
         <v>-6.2300599999999999E-3</v>
@@ -16642,10 +16978,10 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.97361959654178676</v>
+        <v>0.99469308357348707</v>
       </c>
       <c r="C55">
-        <v>0.69580725480434324</v>
+        <v>0.5315229420000035</v>
       </c>
       <c r="H55">
         <v>-1.3653700000000001E-3</v>
@@ -16656,10 +16992,10 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.97856916426512963</v>
+        <v>1.0008645533141212</v>
       </c>
       <c r="C56">
-        <v>0.72389731865171758</v>
+        <v>0.55174940933021954</v>
       </c>
       <c r="H56">
         <v>3.5583400000000001E-3</v>
@@ -16670,10 +17006,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.98313544668587904</v>
+        <v>1.0047478386167146</v>
       </c>
       <c r="C57">
-        <v>0.74797451623518119</v>
+        <v>0.5719758766604357</v>
       </c>
       <c r="H57">
         <v>8.5466699999999993E-3</v>
@@ -16684,10 +17020,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.9873112391930835</v>
+        <v>1.0082175792507204</v>
       </c>
       <c r="C58">
-        <v>0.77606458008255552</v>
+        <v>0.59220234399065164</v>
       </c>
       <c r="H58">
         <v>1.3584000000000001E-2</v>
@@ -16698,10 +17034,10 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.9909510086455332</v>
+        <v>1.0115994236311239</v>
       </c>
       <c r="C59">
-        <v>0.80415464392992952</v>
+        <v>0.61242881132086768</v>
       </c>
       <c r="H59">
         <v>1.8699E-2</v>
@@ -16712,10 +17048,10 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.99428962536023058</v>
+        <v>1.0160100864553314</v>
       </c>
       <c r="C60">
-        <v>0.82823184151339357</v>
+        <v>0.63265527865108384</v>
       </c>
       <c r="H60">
         <v>2.3850799999999998E-2</v>
@@ -16726,10 +17062,10 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.99716282420749269</v>
+        <v>1.018628242074928</v>
       </c>
       <c r="C61">
-        <v>0.85632190536076747</v>
+        <v>0.65288174598129967</v>
       </c>
       <c r="H61">
         <v>2.9101399999999999E-2</v>
@@ -16740,10 +17076,10 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.99969596541786743</v>
+        <v>1.0210158501440922</v>
       </c>
       <c r="C62">
-        <v>0.88441196920814147</v>
+        <v>0.67310821331151571</v>
       </c>
       <c r="H62">
         <v>3.4420600000000003E-2</v>
@@ -16754,10 +17090,10 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>1.001871757925072</v>
+        <v>1.0237002881844379</v>
       </c>
       <c r="C63">
-        <v>0.9125020330555158</v>
+        <v>0.69333468064173209</v>
       </c>
       <c r="H63">
         <v>3.9720400000000003E-2</v>
@@ -16768,10 +17104,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>1.0036239193083574</v>
+        <v>1.0251325648414986</v>
       </c>
       <c r="C64">
-        <v>0.93657923063897941</v>
+        <v>0.71356114797194781</v>
       </c>
       <c r="H64">
         <v>4.5196199999999999E-2</v>
@@ -16782,10 +17118,10 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>1.0049798270893373</v>
+        <v>1.0262824207492796</v>
       </c>
       <c r="C65">
-        <v>0.9646692944863533</v>
+        <v>0.73378761530216419</v>
       </c>
       <c r="H65">
         <v>5.0673599999999999E-2</v>
@@ -16796,10 +17132,10 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>1.0059899135446686</v>
+        <v>1.0270576368876081</v>
       </c>
       <c r="C66">
-        <v>0.99275935833372808</v>
+        <v>0.75401408263238023</v>
       </c>
       <c r="H66">
         <v>5.6217299999999998E-2</v>
@@ -16810,10 +17146,10 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>1.0067622478386167</v>
+        <v>1.0276181556195967</v>
       </c>
       <c r="C67">
-        <v>1.016836555917191</v>
+        <v>0.77424054996259628</v>
       </c>
       <c r="H67">
         <v>6.1918099999999997E-2</v>
@@ -16824,10 +17160,10 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>1.0073011527377522</v>
+        <v>1.0276512968299714</v>
       </c>
       <c r="C68">
-        <v>1.0449266197645659</v>
+        <v>0.79446701729281199</v>
       </c>
       <c r="H68">
         <v>6.7560400000000007E-2</v>
@@ -16838,10 +17174,10 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>1.0076383285302595</v>
+        <v>1.0274452449567724</v>
       </c>
       <c r="C69">
-        <v>1.0730166836119399</v>
+        <v>0.81469348462302837</v>
       </c>
       <c r="H69">
         <v>7.3286299999999999E-2</v>
@@ -16852,10 +17188,10 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>1.0078386167146975</v>
+        <v>1.0271080691642651</v>
       </c>
       <c r="C70">
-        <v>1.1011067474593139</v>
+        <v>0.83491995195324442</v>
       </c>
       <c r="H70">
         <v>7.9195699999999994E-2</v>
@@ -16866,10 +17202,10 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>1.0078804034582134</v>
+        <v>1.0262550432276658</v>
       </c>
       <c r="C71">
-        <v>1.1251839450427781</v>
+        <v>0.85514641928346002</v>
       </c>
       <c r="H71">
         <v>8.51634E-2</v>
@@ -16880,10 +17216,10 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>1.0077507204610952</v>
+        <v>1.0254308357348703</v>
       </c>
       <c r="C72">
-        <v>1.1532740088901521</v>
+        <v>0.87537288661367652</v>
       </c>
       <c r="H72">
         <v>9.1091000000000005E-2</v>
@@ -16894,10 +17230,10 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>1.0075115273775215</v>
+        <v>1.0245129682997118</v>
       </c>
       <c r="C73">
-        <v>1.1813640727375261</v>
+        <v>0.89559935394389245</v>
       </c>
       <c r="H73">
         <v>9.7169199999999997E-2</v>
@@ -16908,10 +17244,10 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>1.0072060518731989</v>
+        <v>1.0228717579250721</v>
       </c>
       <c r="C74">
-        <v>1.20544127032099</v>
+        <v>0.9158258212741085</v>
       </c>
       <c r="H74">
         <v>0.103301</v>
@@ -16922,10 +17258,10 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>1.0068443804034581</v>
+        <v>1.0216729106628242</v>
       </c>
       <c r="C75">
-        <v>1.2335313341683629</v>
+        <v>0.93605228860432454</v>
       </c>
       <c r="H75">
         <v>0.10953599999999999</v>
@@ -16936,10 +17272,10 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>1.0064308357348704</v>
+        <v>1.0203573487031701</v>
       </c>
       <c r="C76">
-        <v>1.261621398015738</v>
+        <v>0.95627875593454059</v>
       </c>
       <c r="H76">
         <v>0.11589000000000001</v>
@@ -16950,10 +17286,10 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>1.0059740634005763</v>
+        <v>1.0189942363112392</v>
       </c>
       <c r="C77">
-        <v>1.2856985955992011</v>
+        <v>0.97650522326475664</v>
       </c>
       <c r="H77">
         <v>0.122154</v>
@@ -16964,10 +17300,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>1.0054971181556196</v>
+        <v>1.0169063400576368</v>
       </c>
       <c r="C78">
-        <v>1.3137886594465751</v>
+        <v>0.99673169059497235</v>
       </c>
       <c r="H78">
         <v>0.12861700000000001</v>
@@ -16978,10 +17314,10 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>1.0050115273775215</v>
+        <v>1.0155216138328531</v>
       </c>
       <c r="C79">
-        <v>1.34187872329395</v>
+        <v>1.016958157925189</v>
       </c>
       <c r="H79">
         <v>0.135075</v>
@@ -16992,10 +17328,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>1.0045259365994237</v>
+        <v>1.0141743515850143</v>
       </c>
       <c r="C80">
-        <v>1.369968787141324</v>
+        <v>1.0371846252554049</v>
       </c>
       <c r="H80">
         <v>0.141682</v>
@@ -17006,10 +17342,10 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>1.0040417867435159</v>
+        <v>1.0128414985590779</v>
       </c>
       <c r="C81">
-        <v>1.394045984724787</v>
+        <v>1.057411092585621</v>
       </c>
       <c r="H81">
         <v>0.148231</v>
@@ -17020,10 +17356,10 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>1.0035662824207494</v>
+        <v>1.0108962536023054</v>
       </c>
       <c r="C82">
-        <v>1.4221360485721619</v>
+        <v>1.077637559915837</v>
       </c>
       <c r="H82">
         <v>0.155061</v>
@@ -17034,10 +17370,10 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>1.0030994236311239</v>
+        <v>1.00964265129683</v>
       </c>
       <c r="C83">
-        <v>1.450226112419537</v>
+        <v>1.0978640272460529</v>
       </c>
       <c r="H83">
         <v>0.16189400000000001</v>
@@ -17048,10 +17384,10 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>1.0026426512968298</v>
+        <v>1.0084409221902018</v>
       </c>
       <c r="C84">
-        <v>1.4743033100030001</v>
+        <v>1.1180904945762691</v>
       </c>
       <c r="H84">
         <v>0.16880600000000001</v>
@@ -17062,10 +17398,10 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>1.0022002881844381</v>
+        <v>1.0067492795389048</v>
       </c>
       <c r="C85">
-        <v>1.5023933738503741</v>
+        <v>1.138316961906485</v>
       </c>
       <c r="H85">
         <v>0.17571000000000001</v>
@@ -17075,6 +17411,12 @@
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>1.0057233429394812</v>
+      </c>
+      <c r="C86">
+        <v>1.158543429236701</v>
+      </c>
       <c r="H86">
         <v>0.18282699999999999</v>
       </c>
@@ -17083,6 +17425,12 @@
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>1.0047881844380404</v>
+      </c>
+      <c r="C87">
+        <v>1.1787698965669171</v>
+      </c>
       <c r="H87">
         <v>0.18990099999999999</v>
       </c>
@@ -17091,6 +17439,12 @@
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>1.0039596541786744</v>
+      </c>
+      <c r="C88">
+        <v>1.198996363897133</v>
+      </c>
       <c r="H88">
         <v>0.19708200000000001</v>
       </c>
@@ -17099,6 +17453,12 @@
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>1.0029149855907782</v>
+      </c>
+      <c r="C89">
+        <v>1.219222831227349</v>
+      </c>
       <c r="H89">
         <v>0.20429600000000001</v>
       </c>
@@ -17107,6 +17467,12 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>1.0023458213256484</v>
+      </c>
+      <c r="C90">
+        <v>1.2394492985575649</v>
+      </c>
       <c r="H90">
         <v>0.21170800000000001</v>
       </c>
@@ -17115,6 +17481,12 @@
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>1.0018703170028818</v>
+      </c>
+      <c r="C91">
+        <v>1.259675765887782</v>
+      </c>
       <c r="H91">
         <v>0.219143</v>
       </c>
@@ -17123,6 +17495,12 @@
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>1.0014755043227666</v>
+      </c>
+      <c r="C92">
+        <v>1.279902233217997</v>
+      </c>
       <c r="H92">
         <v>0.226655</v>
       </c>
@@ -17131,6 +17509,12 @@
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>1.0010576368876081</v>
+      </c>
+      <c r="C93">
+        <v>1.3001287005482129</v>
+      </c>
       <c r="H93">
         <v>0.234206</v>
       </c>
@@ -17139,6 +17523,12 @@
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>1.000884726224784</v>
+      </c>
+      <c r="C94">
+        <v>1.3203551678784291</v>
+      </c>
       <c r="H94">
         <v>0.2419</v>
       </c>
@@ -17147,6 +17537,12 @@
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>1.0007853025936599</v>
+      </c>
+      <c r="C95">
+        <v>1.3405816352086459</v>
+      </c>
       <c r="H95">
         <v>0.24962000000000001</v>
       </c>
@@ -17155,6 +17551,12 @@
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>1.0007838616714697</v>
+      </c>
+      <c r="C96">
+        <v>1.360808102538861</v>
+      </c>
       <c r="H96">
         <v>0.25750000000000001</v>
       </c>
@@ -17162,7 +17564,13 @@
         <v>-0.27952038760955961</v>
       </c>
     </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>1.0008731988472623</v>
+      </c>
+      <c r="C97">
+        <v>1.381034569869078</v>
+      </c>
       <c r="H97">
         <v>0.26537899999999998</v>
       </c>
@@ -17170,7 +17578,13 @@
         <v>-0.27547226305188077</v>
       </c>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>1.0010288184438041</v>
+      </c>
+      <c r="C98">
+        <v>1.401261037199294</v>
+      </c>
       <c r="H98">
         <v>0.27336700000000003</v>
       </c>
@@ -17178,7 +17592,13 @@
         <v>-0.27142359409875327</v>
       </c>
     </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99">
+        <v>1.0012420749279538</v>
+      </c>
+      <c r="C99">
+        <v>1.421487504529509</v>
+      </c>
       <c r="H99">
         <v>0.28140100000000001</v>
       </c>
@@ -17186,7 +17606,13 @@
         <v>-0.26737546954107461</v>
       </c>
     </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100">
+        <v>1.001657060518732</v>
+      </c>
+      <c r="C100">
+        <v>1.4417139718597261</v>
+      </c>
       <c r="H100">
         <v>0.28958200000000001</v>
       </c>
@@ -17194,7 +17620,13 @@
         <v>-0.26332734498339588</v>
       </c>
     </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B101">
+        <v>1.0019942363112393</v>
+      </c>
+      <c r="C101">
+        <v>1.461940439189942</v>
+      </c>
       <c r="H101">
         <v>0.29775299999999999</v>
       </c>
@@ -17202,7 +17634,13 @@
         <v>-0.25927867603026838</v>
       </c>
     </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102">
+        <v>1.0023559077809798</v>
+      </c>
+      <c r="C102">
+        <v>1.482166906520157</v>
+      </c>
       <c r="H102">
         <v>0.30603000000000002</v>
       </c>
@@ -17210,7 +17648,13 @@
         <v>-0.25523055147258972</v>
       </c>
     </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103">
+        <v>1.0027319884726225</v>
+      </c>
+      <c r="C103">
+        <v>1.5023933738503741</v>
+      </c>
       <c r="H103">
         <v>0.31434099999999998</v>
       </c>
@@ -17218,7 +17662,7 @@
         <v>-0.25118188251946222</v>
       </c>
     </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H104">
         <v>0.32283499999999998</v>
       </c>
@@ -17226,7 +17670,7 @@
         <v>-0.24713375796178341</v>
       </c>
     </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H105">
         <v>0.33135500000000001</v>
       </c>
@@ -17234,7 +17678,7 @@
         <v>-0.2430856334041048</v>
       </c>
     </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H106">
         <v>0.339922</v>
       </c>
@@ -17242,7 +17686,7 @@
         <v>-0.23903696445097719</v>
       </c>
     </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H107">
         <v>0.34862500000000002</v>
       </c>
@@ -17250,7 +17694,7 @@
         <v>-0.23498883989329841</v>
       </c>
     </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H108">
         <v>0.35735800000000001</v>
       </c>
@@ -17258,7 +17702,7 @@
         <v>-0.23094017094017091</v>
       </c>
     </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H109">
         <v>0.36626199999999998</v>
       </c>
@@ -17266,7 +17710,7 @@
         <v>-0.22689204638249219</v>
       </c>
     </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H110">
         <v>0.37513400000000002</v>
       </c>
@@ -17274,7 +17718,7 @@
         <v>-0.22284392182481361</v>
       </c>
     </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H111">
         <v>0.38401600000000002</v>
       </c>
@@ -17282,7 +17726,7 @@
         <v>-0.218795252871686</v>
       </c>
     </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H112">
         <v>0.392901</v>
       </c>
